--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -244,11 +244,6 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="B19" authorId="0" shapeId="0">
-      <text>
-        <t>旧事業所の内容のまま。要確認</t>
-      </text>
-    </comment>
     <comment ref="B22" authorId="0" shapeId="0">
       <text>
         <t>原本の「指定本文介護」は「指定訪問介護」の誤字と思われます（原本のまま）</t>
@@ -744,7 +739,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>大阪市西淀川区、大阪市淀川区、東淀川区</t>
+          <t>大阪市西淀川区、大阪市淀川区、東淀川区、天王寺区、中央区、北区</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -4755,7 +4750,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>旧事業所の内容をそのまま残した箇所（実施地域・損害賠償保険など）。要確認</t>
+          <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重要事項説明書" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="契約書" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人情報使用同意書" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +62,25 @@
       <name val="Arial"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -96,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -155,6 +175,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -4673,6 +4711,528 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>情報管理規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における情報資産を適正に管理し、秘密情報及び個人情報の漏えい、不正使用、毀損を防止し、事業活動の信頼性と従業員の職務上の責務を明確にすることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。役員、派遣社員、業務委託先等の関係者についても、会社が必要と認める場合は適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>第2章　情報の取扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>（秘密情報の範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>第3条　秘密情報とは、会社の業務に関し公知でない情報をいう。営業情報、技術情報、顧客情報、従業員の人事・給与情報、財務情報等を含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>（個人情報の範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>第4条　個人情報とは、個人を識別できる情報（氏名、住所、電話番号、メールアドレス、健康情報等）をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>（利用目的の限定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>第5条　従業員は、秘密情報及び個人情報を、業務遂行の目的の範囲内でのみ利用しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>（持ち出し・複製の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>第6条　従業員は、会社の承認なく情報資産を持ち出し、複製し、または外部に提供してはならない。やむを得ず持ち出す場合は、上長の承認を受けるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>（電子機器・通信利用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>第7条　従業員は、会社支給のPC、スマートフォン、メールアカウント等を業務目的以外に利用してはならない。私的利用、違法・不適切なサイト閲覧、外部クラウドサービスへの無断保存は禁止する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="8" customHeight="1">
+      <c r="A51" s="28" t="inlineStr"/>
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="12" t="n"/>
+    </row>
+    <row r="52" ht="10" customHeight="1"/>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>第3章　管理体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>（管理責任者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>第8条　会社は、情報管理責任者を置き、情報資産の保護・管理を統括させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>（アクセス管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>第9条　会社は、情報システムへのアクセス権限を職務に応じて付与し、不要となった場合は速やかに停止する。従業員は、他人のID・パスワードを使用してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>（媒体管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>第10条　USBメモリ、外付HDD、紙媒体等の外部記録媒体の利用は会社の許可を要する。利用後は速やかに返却・廃棄しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>（廃棄時の管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>第11条　秘密情報及び個人情報を含む文書、媒体を廃棄する場合は、会社所定の方法（シュレッダー、専用廃棄サービス等）に従わなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="8" customHeight="1"/>
+    <row r="66" ht="8" customHeight="1">
+      <c r="A66" s="28" t="inlineStr"/>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="n"/>
+      <c r="E66" s="12" t="n"/>
+    </row>
+    <row r="67" ht="10" customHeight="1"/>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>第4章　従業員の義務</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>（秘密保持義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、在職中及び退職後においても、秘密情報及び個人情報を漏らしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="26" t="inlineStr">
+        <is>
+          <t>（退職時の返還）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、退職時に会社から貸与された機器、資料、データ等をすべて返還し、社内システムへのアクセス権を消去しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>（事故報告義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>第14条　従業員は、情報の漏えい、紛失、改ざん、マルウェア感染等の事故を知ったときは、直ちに会社に報告しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="26" t="inlineStr">
+        <is>
+          <t>（ソーシャルメディア利用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>第15条　従業員は、SNS、掲示板、ブログ等を利用する際に、会社や取引先の秘密情報・個人情報を投稿・公開してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="8" customHeight="1">
+      <c r="A81" s="28" t="inlineStr"/>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+    </row>
+    <row r="82" ht="10" customHeight="1"/>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>第5章　教育・監査</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
+          <t>（教育）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>第16条　会社は、従業員に対して情報管理及び個人情報保護に関する教育を定期的に実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>（監査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、必要に応じて情報管理状況の監査を行い、改善を指示できる。従業員は監査に協力しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="8" customHeight="1">
+      <c r="A90" s="28" t="inlineStr"/>
+      <c r="B90" s="12" t="n"/>
+      <c r="C90" s="12" t="n"/>
+      <c r="D90" s="12" t="n"/>
+      <c r="E90" s="12" t="n"/>
+    </row>
+    <row r="91" ht="10" customHeight="1"/>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="25" t="inlineStr">
+        <is>
+          <t>第6章　罰則</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>（懲戒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>第18条　従業員が本規程に違反した場合は、「懲戒規程」に基づき懲戒処分の対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>2　会社に損害が生じた場合は、法令に基づき賠償責任を負うことがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="8" customHeight="1">
+      <c r="A97" s="28" t="inlineStr"/>
+      <c r="B97" s="12" t="n"/>
+      <c r="C97" s="12" t="n"/>
+      <c r="D97" s="12" t="n"/>
+      <c r="E97" s="12" t="n"/>
+    </row>
+    <row r="98" ht="10" customHeight="1"/>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　情報管理規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>
@@ -4683,96 +5243,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>法人名</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>ええかいご → いいかいご（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>管理者・サービス提供責任者等</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>要入力</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>なし（すべて入力済み）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>コメント付きセル</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>説明年月日・利用者欄</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>新しく使えるよう空欄にしています</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>元の資料</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
         </is>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="契約書" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人情報使用同意書" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -116,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,6 +194,18 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -5233,6 +5246,772 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>出張旅費規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の役員及び従業員が業務上出張する際に要する旅費の支給基準を定め、業務の円滑な遂行と経済性の確保、並びに適正な経費管理を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社の業務命令により出張する役員及び従業員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>2　研修、出向その他特別の事情については、別途定めがある場合を優先する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>第3条　本規程において「出張」とは、所属事業所の所在地を離れて業務に従事することをいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程において「旅費」とは、交通費、宿泊料及び日当をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="8" customHeight="1">
+      <c r="A38" s="28" t="inlineStr"/>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="10" customHeight="1"/>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>第2章　国内出張</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>（交通費）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>第4条　国内出張に要する交通費は、原則として公共交通機関の普通運賃の実費を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>2　航空機の利用は、会社が事前に承認した場合に限り、最も経済的かつ合理的な経路・料金に基づき支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>3　自家用車を使用した場合は、会社が定める距離単価（1kmあたり15円）を上限として支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>4　タクシーの利用は、早朝・深夜、交通の便が著しく不便な場合、または荷物の運搬等やむを得ないと会社が認めた場合に限り、実費を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>（宿泊料）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>第5条　宿泊を伴う出張の場合の宿泊料の上限は、役職ごとに次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="inlineStr">
+        <is>
+          <t>宿泊料上限（1泊）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>役員</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>20,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>部長</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>15,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>次長</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>13,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>リーダー・責任者</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>12,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t>一般従業員</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>10,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="8" customHeight="1"/>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>2　宿泊地の実情により上限を超えることが避けられない場合は、所属長の承認を得て実費を支給できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>（日当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>第6条　出張に従事した者には、宿泊・日帰りを問わず、役職に応じて次のとおり日当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>日当（1日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>役員</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>4,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>部長</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>3,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>次長</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>2,500円</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>リーダー・責任者</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="inlineStr">
+        <is>
+          <t>2,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>一般従業員</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="inlineStr">
+        <is>
+          <t>1,500円</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>2　出張が半日に満たない場合、または会社が特に必要と認めない場合は、日当を支給しないことがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="8" customHeight="1">
+      <c r="A69" s="28" t="inlineStr"/>
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="12" t="n"/>
+      <c r="D69" s="12" t="n"/>
+      <c r="E69" s="12" t="n"/>
+    </row>
+    <row r="70" ht="10" customHeight="1"/>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>第3章　海外出張</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="26" t="inlineStr">
+        <is>
+          <t>（旅費の原則）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>第7条　海外出張に要する旅費は、原則として実費を支給する。ただし、宿泊料及び日当については、次条の上限を適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>（宿泊料・日当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>第8条　海外出張における宿泊料及び日当の上限は、地域区分ごとに次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>宿泊料上限（1泊）</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>日当（1日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>北米・欧州</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="inlineStr">
+        <is>
+          <t>30,000円</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>5,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>アジア主要都市</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>20,000円</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>4,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>アジアその他</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>15,000円</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>3,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>その他地域</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="inlineStr">
+        <is>
+          <t>18,000円</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>3,500円</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="8" customHeight="1"/>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>2　宿泊地の物価水準や治安、業務遂行上の必要性により上限を超えることが避けられない場合は、代表取締役の承認を得て実費を支給できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
+          <t>（航空運賃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>第9条　海外出張における航空運賃は、原則としてエコノミークラスの実費とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>2　役員が長時間の移動を伴う場合や特別の事情がある場合は、所属長の承認を得てビジネスクラスを利用できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="8" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="26" t="inlineStr">
+        <is>
+          <t>（仮払・精算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>第10条　海外出張に際しては、必要に応じて現地通貨による仮払を行うことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>2　出張を終えた者は、帰国後7日以内に旅費精算書を提出し、領収書等を添付して精算しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="8" customHeight="1">
+      <c r="A93" s="28" t="inlineStr"/>
+      <c r="B93" s="12" t="n"/>
+      <c r="C93" s="12" t="n"/>
+      <c r="D93" s="12" t="n"/>
+      <c r="E93" s="12" t="n"/>
+    </row>
+    <row r="94" ht="10" customHeight="1"/>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="25" t="inlineStr">
+        <is>
+          <t>第4章　精算・手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="26" t="inlineStr">
+        <is>
+          <t>（仮払申請）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>第11条　国内外を問わず、出張に際して旅費の仮払を受けようとする者は、所定の様式により申請し、所属長及び経理部門の承認を得なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="26" t="inlineStr">
+        <is>
+          <t>（精算義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>第12条　出張を終えた者は、速やかに旅費精算書を提出し、領収書等の証憑を添付して精算しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>2　精算期限は原則として出張終了後7日以内とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>（例外規定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>第13条　本規程に定める基準により業務遂行が著しく困難な場合、または会社が必要と認めた場合は、代表取締役の承認を得て例外的な取扱いを行うことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="8" customHeight="1">
+      <c r="A106" s="28" t="inlineStr"/>
+      <c r="B106" s="12" t="n"/>
+      <c r="C106" s="12" t="n"/>
+      <c r="D106" s="12" t="n"/>
+      <c r="E106" s="12" t="n"/>
+    </row>
+    <row r="107" ht="10" customHeight="1"/>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="25" t="inlineStr">
+        <is>
+          <t>第5章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>（不正受給の禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>第14条　虚偽の申請その他不正な手段により旅費を受給した者は、会社の請求によりその全額を返還し、併せて懲戒規程に基づき処分の対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>（周知義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>第15条　会社は、本規程の内容を役員及び従業員に周知し、常時確認できるようにしなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="8" customHeight="1">
+      <c r="A115" s="28" t="inlineStr"/>
+      <c r="B115" s="12" t="n"/>
+      <c r="C115" s="12" t="n"/>
+      <c r="D115" s="12" t="n"/>
+      <c r="E115" s="12" t="n"/>
+    </row>
+    <row r="116" ht="10" customHeight="1"/>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="57">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　出張旅費規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>
@@ -5243,96 +6022,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>法人名</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>ええかいご → いいかいご（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>管理者・サービス提供責任者等</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>要入力</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>なし（すべて入力済み）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>コメント付きセル</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>説明年月日・利用者欄</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>新しく使えるよう空欄にしています</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>元の資料</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
         </is>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人情報使用同意書" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6012,6 +6013,617 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>安全衛生規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における労働安全衛生を確保し、従業員の安全と健康を保持するとともに、快適な職場環境を形成するために必要な事項を定めることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。派遣社員、嘱託社員、アルバイト等の従業員についても、会社が必要と認める範囲で適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>第2章　安全衛生管理体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>（責任体制）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>第3条　会社は、安全衛生管理の責任者として代表取締役を安全衛生統括管理者とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>2　統括管理者は、安全衛生に関する基本方針を策定し、その実施を統括する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>（衛生推進者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>第4条　会社は、常時50人未満の事業場であるため法令上の衛生管理者選任義務はないが、必要に応じて衛生推進者を指名し、従業員の健康保持増進活動を推進することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="8" customHeight="1">
+      <c r="A43" s="28" t="inlineStr"/>
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+    </row>
+    <row r="44" ht="10" customHeight="1"/>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>第3章　健康管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>（健康診断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>第5条　会社は、労働安全衛生法に基づき、従業員に次の健康診断を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>1　雇入時健康診断（入社時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>2　定期健康診断（年1回。ただし夜勤業務に従事する者については年2回）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>3　特定業務従事者健康診断（必要に応じて）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>2　健康診断の費用は会社が負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>（診断結果への対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>第6条　会社は、健康診断の結果に基づき、必要に応じて就業上の措置を講じる。従業員は医師の意見に従い、就業制限や治療を受けなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="8" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>（ストレスチェック）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>第7条　会社は、従業員数50人未満のため法定義務はないが、必要に応じてストレスチェックを実施し、結果に基づき職場環境改善や個別対応を行うことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="8" customHeight="1"/>
+    <row r="59" ht="8" customHeight="1">
+      <c r="A59" s="28" t="inlineStr"/>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12" t="n"/>
+    </row>
+    <row r="60" ht="10" customHeight="1"/>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>第4章　職場環境の整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t>（作業環境管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>第8条　会社は、職場の換気、採光、照明、温度、騒音等の環境を適正に維持する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>（作業方法の改善）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>第9条　会社は、業務に伴う危険や健康障害を防止するため、作業方法を改善し、安全衛生教育を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>2　特に介護業務においては、腰痛予防、福祉用具の適切な使用、送迎業務における車両運転の安全確保に努める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>（感染症予防）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>第10条　会社は、インフルエンザ、新型コロナウイルスその他感染症の予防に努め、必要に応じてマスク着用、手指消毒、在宅勤務、出勤停止等の措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="8" customHeight="1">
+      <c r="A72" s="28" t="inlineStr"/>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="12" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+    </row>
+    <row r="73" ht="10" customHeight="1"/>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>第5章　安全衛生教育</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>（教育の実施）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>第11条　会社は、従業員に対して次の安全衛生教育を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>1　雇入時教育（安全衛生に関する基本事項）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>2　配置転換時教育（新しい業務に伴う危険防止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>3　作業内容変更時教育（介護・送迎業務における腰痛防止、交通安全等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>4　定期教育（年1回以上、安全衛生全般に関する教育）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="8" customHeight="1">
+      <c r="A82" s="28" t="inlineStr"/>
+      <c r="B82" s="12" t="n"/>
+      <c r="C82" s="12" t="n"/>
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="12" t="n"/>
+    </row>
+    <row r="83" ht="10" customHeight="1"/>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="25" t="inlineStr">
+        <is>
+          <t>第6章　労働災害への対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
+          <t>（災害発生時の措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>第12条　労働災害が発生した場合、従業員は直ちに上長に報告し、会社は応急措置を講じ、必要に応じて関係行政官庁へ報告する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="8" customHeight="1"/>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="26" t="inlineStr">
+        <is>
+          <t>（再発防止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>第13条　会社は、労働災害が発生した場合、その原因を調査し、再発防止策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="8" customHeight="1"/>
+    <row r="91" ht="8" customHeight="1">
+      <c r="A91" s="28" t="inlineStr"/>
+      <c r="B91" s="12" t="n"/>
+      <c r="C91" s="12" t="n"/>
+      <c r="D91" s="12" t="n"/>
+      <c r="E91" s="12" t="n"/>
+    </row>
+    <row r="92" ht="10" customHeight="1"/>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="25" t="inlineStr">
+        <is>
+          <t>第7章　健康保持・メンタルヘルス</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="26" t="inlineStr">
+        <is>
+          <t>（過重労働対策）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>第14条　会社は、時間外労働や深夜労働が従業員の心身に過度の負担を与えないように管理し、長時間労働が認められる場合は速やかに対応する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>（メンタルヘルス対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>第15条　会社は、従業員がうつ病、適応障害その他のメンタル不調を抱えた場合、医師の診断や専門家の意見を踏まえ、必要な就業上の措置（休職・勤務軽減・復職支援等）を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="8" customHeight="1">
+      <c r="A100" s="28" t="inlineStr"/>
+      <c r="B100" s="12" t="n"/>
+      <c r="C100" s="12" t="n"/>
+      <c r="D100" s="12" t="n"/>
+      <c r="E100" s="12" t="n"/>
+    </row>
+    <row r="101" ht="10" customHeight="1"/>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="25" t="inlineStr">
+        <is>
+          <t>第8章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>（健康情報の管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>第16条　健康診断やストレスチェックの結果、相談等により得た従業員の個人情報は厳格に管理し、本人の同意なく第三者に開示してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="26" t="inlineStr">
+        <is>
+          <t>（不利益取扱いの禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、従業員が健康診断、感染症予防措置、安全衛生教育等を受けたことを理由に、不利益取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="8" customHeight="1"/>
+    <row r="109" ht="8" customHeight="1">
+      <c r="A109" s="28" t="inlineStr"/>
+      <c r="B109" s="12" t="n"/>
+      <c r="C109" s="12" t="n"/>
+      <c r="D109" s="12" t="n"/>
+      <c r="E109" s="12" t="n"/>
+    </row>
+    <row r="110" ht="10" customHeight="1"/>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、労働基準法、労働安全衛生法その他関係法令による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="66">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　安全衛生規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6624,6 +6625,669 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E116"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>懲戒規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における服務規律を確立し、職場秩序の維持及び業務の円滑な運営を図るため、懲戒処分の種類、事由及び手続を定めることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>（基本原則）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>第3条　懲戒処分は、法令及び社会通念に照らし合理的かつ相当と認められる範囲で行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>2　処分にあたっては、従業員の行為の態様、動機、過去の勤務態度及び会社への影響を総合的に考慮する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>3　軽微な違反については、まず指導や注意を行い、改善が見られない場合に段階的に処分を適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="8" customHeight="1">
+      <c r="A38" s="28" t="inlineStr"/>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="10" customHeight="1"/>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>第2章　懲戒の種類</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>（懲戒の段階）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>第4条　懲戒の種類は、次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>1　口頭注意：軽微な規律違反について、口頭で注意し改善を促す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>2　始末書提出：違反行為に対し、始末書の提出を命じ、反省を促す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>3　譴責（けんせき）：文書により将来を戒め、人事記録に残す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>4　減給：労働基準法第91条に基づき、1回の額は平均賃金の1日分の半額以内、かつ1賃金支払期における総額は賃金総額の10分の1以内とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>5　出勤停止：一定期間（最長10日間）就業を禁止する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>6　降格：役職解任または等級引下げを行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>7　諭旨解雇：本人の反省状況を踏まえ、退職を勧奨する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>8　懲戒解雇：重大な背信行為があり、雇用関係の継続が著しく困難な場合に行う解雇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="8" customHeight="1"/>
+    <row r="52" ht="8" customHeight="1">
+      <c r="A52" s="28" t="inlineStr"/>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+    </row>
+    <row r="53" ht="10" customHeight="1"/>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>第3章　懲戒事由</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>（勤務態度・職務遂行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>第5条　従業員が次の各号に該当する場合、懲戒処分に付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>1　無断欠勤が連続3日以上に及ぶ場合、または度重なる遅刻・早退・欠勤を繰り返した場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>2　正当な理由なく業務上の指示命令に従わない場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>3　勤務態度が著しく不良で職場秩序を乱した場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>4　虚偽の申告や報告を行った場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t>（ハラスメント行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>第6条　従業員が次の行為を行った場合は、懲戒処分に付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>1　セクシュアルハラスメント、パワーハラスメント、マタニティハラスメントその他のハラスメント行為。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>2　ハラスメント申告者に対する不利益取扱いや報復行為。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>（会社財産・情報関連）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>第7条　従業員が次の行為を行った場合は、懲戒処分に付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>1　会社の金品・備品を横領・窃取・毀損した場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>2　会社の秘密情報または個人情報を漏洩、不正利用した場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>3　SNSその他インターネット上において会社の信用を著しく毀損する行為を行った場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="26" t="inlineStr">
+        <is>
+          <t>（重大違反行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>第8条　従業員が次の行為を行った場合は、原則として懲戒解雇に付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>1　横領、背任、詐欺その他重大な不正行為を行った場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>2　傷害、脅迫、窃盗等、刑法その他法令に違反し刑事罰に該当する行為を行った場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>3　禁錮以上の刑に処せられ、その判決が確定した場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>4　無断で会社と競合する事業に従事した場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>5　会社に重大な損害を与えた場合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="8" customHeight="1">
+      <c r="A81" s="28" t="inlineStr"/>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+    </row>
+    <row r="82" ht="10" customHeight="1"/>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>第4章　懲戒の手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
+          <t>（調査と弁明の機会）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>第9条　会社は懲戒処分を科すにあたり、事実関係を調査し、当該従業員に弁明の機会を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>（決定手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>第10条　懲戒処分は、上長、人事部門責任者その他会社が指名する者による協議を経て、代表取締役が決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>（通知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>第11条　懲戒処分は、書面により通知し、処分理由、処分内容及び発効日を明示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>（不服申立て）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は懲戒処分に不服がある場合、通知を受けた日から7日以内に人事部門に不服申立てを行うことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="8" customHeight="1">
+      <c r="A96" s="28" t="inlineStr"/>
+      <c r="B96" s="12" t="n"/>
+      <c r="C96" s="12" t="n"/>
+      <c r="D96" s="12" t="n"/>
+      <c r="E96" s="12" t="n"/>
+    </row>
+    <row r="97" ht="10" customHeight="1"/>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="25" t="inlineStr">
+        <is>
+          <t>第5章　退職金との関係</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="26" t="inlineStr">
+        <is>
+          <t>（退職金の不支給）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員が懲戒解雇となった場合で、重大な背信行為により会社に著しい損害を与えたときは、退職金の全部または一部を支給しないことがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>2　退職金の不支給・減額については、退職金規程に基づき、具体的事由及び手続きを経て決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="8" customHeight="1">
+      <c r="A103" s="28" t="inlineStr"/>
+      <c r="B103" s="12" t="n"/>
+      <c r="C103" s="12" t="n"/>
+      <c r="D103" s="12" t="n"/>
+      <c r="E103" s="12" t="n"/>
+    </row>
+    <row r="104" ht="10" customHeight="1"/>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="25" t="inlineStr">
+        <is>
+          <t>第6章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="26" t="inlineStr">
+        <is>
+          <t>（二重処分の禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>第14条　同一の事由について二重に懲戒処分を行ってはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="8" customHeight="1"/>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>（記録の取扱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>第15条　懲戒処分の記録は、一定期間経過後に従業員の勤務態度が改善された場合、人事記録から削除することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="8" customHeight="1">
+      <c r="A112" s="28" t="inlineStr"/>
+      <c r="B112" s="12" t="n"/>
+      <c r="C112" s="12" t="n"/>
+      <c r="D112" s="12" t="n"/>
+      <c r="E112" s="12" t="n"/>
+    </row>
+    <row r="113" ht="10" customHeight="1"/>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、労働基準法、労働契約法その他関係法令による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="73">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　懲戒規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7288,6 +7289,470 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>表彰規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）において、模範的な勤務態度、業績、功績を挙げた従業員を表彰し、その功労をたたえることにより、従業員の士気を高め、会社の発展に資することを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>第2章　表彰の種類</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>（種類）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>第3条　表彰の種類は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>1　永年勤続表彰：30年間継続して勤務した者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>2　功労表彰：業務上著しい功績を挙げ、会社に大きく貢献した者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>3　精勤表彰：勤務成績が優秀で、服務規律を遵守し、同僚の模範となった者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>4　善行表彰：社会貢献、災害救助、安全確保等に顕著な功績を示した者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>5　特別表彰：上記に該当しないが、会社が特に認める功績を挙げた者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>6　社長賞（特別功労表彰）：経営方針や会社の発展に特に寄与した功績が顕著で、代表取締役が自ら選定し表彰する者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="8" customHeight="1">
+      <c r="A45" s="28" t="inlineStr"/>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="12" t="n"/>
+    </row>
+    <row r="46" ht="10" customHeight="1"/>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>第3章　表彰の基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>（基準）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>第4条　表彰の基準は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>1　永年勤続表彰は、勤続30年に達した者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>2　功労表彰は、売上拡大・業務改善・顧客満足向上等により会社に特段の利益をもたらした者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>3　精勤表彰は、無事故・無違反・皆勤等を通じて勤務成績が特に優秀である者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>4　善行表彰は、業務内外で会社の社会的評価を高める行為を行った者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>5　特別表彰は、業務改善提案、CSR活動、チームへの貢献など、会社が必要と認める行為を行った者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>6　社長賞は、会社の将来に影響を与える顕著な功績を挙げた者、または特別な成果を出した者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="8" customHeight="1">
+      <c r="A57" s="28" t="inlineStr"/>
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="12" t="n"/>
+      <c r="D57" s="12" t="n"/>
+      <c r="E57" s="12" t="n"/>
+    </row>
+    <row r="58" ht="10" customHeight="1"/>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>第4章　表彰の手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>（推薦及び決定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>第5条　表彰候補者は、所属長の推薦または人事部門の審査により選考する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>2　社長賞については、代表取締役が自ら選定することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>3　表彰の決定は、表彰委員会の審議を経て代表取締役が行う。ただし、社長賞についてはこの限りでない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>（表彰方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>第6条　表彰は、表彰状及び副賞の授与により行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>2　副賞の内容は、金一封、記念品その他の方法とし、その範囲や金額については会社が別途定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>（表彰の時期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>第7条　表彰は、原則として年1回開催される全社行事において行う。ただし、社長賞その他特別の表彰については、随時実施できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="8" customHeight="1">
+      <c r="A72" s="28" t="inlineStr"/>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="12" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+    </row>
+    <row r="73" ht="10" customHeight="1"/>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>第5章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>（社外公表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>第8条　会社は、受賞者の同意を得たうえで、表彰内容を社内外に公表することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="26" t="inlineStr">
+        <is>
+          <t>（取消し）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>第9条　表彰を受けた者が、その後不正行為や服務違反により懲戒処分を受けたときは、会社は表彰を取り消すことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="8" customHeight="1">
+      <c r="A81" s="28" t="inlineStr"/>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+    </row>
+    <row r="82" ht="10" customHeight="1"/>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　表彰規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3576,6 +3577,120 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>法人名</t>
+        </is>
+      </c>
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>ええかいご → いいかいご（ご指示どおり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>管理者・サービス提供責任者等</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>要入力</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>なし（すべて入力済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>コメント付きセル</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>説明年月日・利用者欄</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>新しく使えるよう空欄にしています</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>元の資料</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7753,112 +7868,755 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="33" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B1" s="33" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="34" t="inlineStr">
-        <is>
-          <t>法人名</t>
-        </is>
-      </c>
-      <c r="B2" s="34" t="inlineStr">
-        <is>
-          <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="34" t="inlineStr">
-        <is>
-          <t>事業所名</t>
-        </is>
-      </c>
-      <c r="B3" s="34" t="inlineStr">
-        <is>
-          <t>ええかいご → いいかいご（ご指示どおり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>管理者・サービス提供責任者等</t>
-        </is>
-      </c>
-      <c r="B4" s="34" t="inlineStr">
-        <is>
-          <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>要入力</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>なし（すべて入力済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>コメント付きセル</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>説明年月日・利用者欄</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>新しく使えるよう空欄にしています</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>元の資料</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>休暇規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に付与される休暇に関する事項を定め、労働基準法その他関係法令を遵守しつつ、従業員の心身の健康保持と円滑な業務運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、嘱託社員、短時間勤務者、アルバイト等については、就業形態に応じて別途定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>第2章　年次有給休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>（付与要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>第3条　会社は、継続勤務6か月を経過し、その期間の全労働日の8割以上出勤した従業員に対し、10日の年次有給休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>2　その後も、継続勤務ごとに6か月経過するごとに10日の年次有給休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>（取得方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>（時季変更権）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="8" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>（時間単位年休）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇の一部を時間単位で取得させることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>（計画的付与）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="8" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t>（年5日の取得義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="8" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>（有効期限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
+    <row r="61" ht="8" customHeight="1">
+      <c r="A61" s="28" t="inlineStr"/>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+    </row>
+    <row r="62" ht="10" customHeight="1"/>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>第3章　特別休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="26" t="inlineStr">
+        <is>
+          <t>（慶弔休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>1　本人の結婚：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>2　子女の結婚：2日</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>3　配偶者の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>4　父母・子の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>6　その他会社が必要と認めた場合：別途定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="26" t="inlineStr">
+        <is>
+          <t>（産前産後休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>（育児休業・介護休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>（子の看護休暇・介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、小学校就学前の子1人につき年間5日（2人以上は10日）の子の看護休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>2　要介護家族については、年間5日の介護休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
+          <t>（病気休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>（公務・公用休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>（感染症予防に伴う休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>（誕生日休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="27" t="inlineStr">
+        <is>
+          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="26" t="inlineStr">
+        <is>
+          <t>（その他の特別休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="8" customHeight="1"/>
+    <row r="101" ht="8" customHeight="1">
+      <c r="A101" s="28" t="inlineStr"/>
+      <c r="B101" s="12" t="n"/>
+      <c r="C101" s="12" t="n"/>
+      <c r="D101" s="12" t="n"/>
+      <c r="E101" s="12" t="n"/>
+    </row>
+    <row r="102" ht="10" customHeight="1"/>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="25" t="inlineStr">
+        <is>
+          <t>第4章　手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="26" t="inlineStr">
+        <is>
+          <t>（申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="8" customHeight="1"/>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="26" t="inlineStr">
+        <is>
+          <t>（診断書等の提出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>1　私傷病により連続して3日以上欠勤するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>2　休職を申請するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>5　会社が安全衛生管理上必要と認めたとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="8" customHeight="1">
+      <c r="A120" s="28" t="inlineStr"/>
+      <c r="B120" s="12" t="n"/>
+      <c r="C120" s="12" t="n"/>
+      <c r="D120" s="12" t="n"/>
+      <c r="E120" s="12" t="n"/>
+    </row>
+    <row r="121" ht="10" customHeight="1"/>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="25" t="inlineStr">
+        <is>
+          <t>第5章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="26" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="8" customHeight="1"/>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="26" t="inlineStr">
+        <is>
+          <t>（休暇中の待遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="8" customHeight="1"/>
+    <row r="129" ht="8" customHeight="1">
+      <c r="A129" s="28" t="inlineStr"/>
+      <c r="B129" s="12" t="n"/>
+      <c r="C129" s="12" t="n"/>
+      <c r="D129" s="12" t="n"/>
+      <c r="E129" s="12" t="n"/>
+    </row>
+    <row r="130" ht="10" customHeight="1"/>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="84">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　休暇規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3581,6 +3582,1169 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E192"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>福利厚生規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における福利厚生制度に関し必要な事項を定め、従業員の生活の安定と向上、健康保持、能力開発及び職場環境の充実を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての正社員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>2　契約社員、嘱託社員、パートタイマー等については、雇用契約書において別途定めがある場合を除き、本規程を準用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="8" customHeight="1">
+      <c r="A34" s="28" t="inlineStr"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="10" customHeight="1"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>第2章　法定福利厚生</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>（社会保険）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>第3条　会社は、健康保険、厚生年金保険、雇用保険及び労災保険の適用事業所として、法令に基づき従業員を加入させ、会社負担分の保険料を負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="8" customHeight="1">
+      <c r="A40" s="28" t="inlineStr"/>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="10" customHeight="1"/>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>第3章　通勤手当</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>（支給対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>第4条　会社は、従業員の通勤に要する費用について、次の範囲内で通勤手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>1　公共交通機関を利用する場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>2　片道2km以上の自動車・バイクによる通勤</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>3　自転車による通勤</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>4　その他事前申請の上会社が認めた通勤方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="8" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>（支給基準および額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>第5条　通勤手当の支給額は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t>1　公共交通機関の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>（1）定期券を購入している場合はその額</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>（2）定期券を購入していない場合は、実費または1か月分の定期代相当額</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>ただし、いずれの場合も上限は月額50,000円とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>2　自動車・バイクによる場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>（1）往復距離 × 出勤日数 × 20円</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>（2）月額の上限は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>片道距離</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>上限（月額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>2km以上10km未満</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>4,200円</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>10km以上15km未満</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>7,100円</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>15km以上25km未満</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>12,900円</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>25km以上35km未満</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="inlineStr">
+        <is>
+          <t>18,700円</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>35km以上45km未満</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="inlineStr">
+        <is>
+          <t>24,400円</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>45km以上55km未満</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="inlineStr">
+        <is>
+          <t>28,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>55km以上</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="inlineStr">
+        <is>
+          <t>31,600円</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>3　自転車による場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>（1）1日あたり100円 × 出勤日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>（2）月額上限は2,500円とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="26" t="inlineStr">
+        <is>
+          <t>4　その他事前申請の上会社が認めた通勤方法の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>会社が合理的と認める方法により算出する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
+          <t>（申請・承認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>第6条　通勤手当の支給を受けるには、従業員が所定の様式により通勤方法、経路、実費額を申請し、会社の承認を得なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>2　通勤経路が複数ある場合、会社は合理的かつ経済的と認められる経路を通勤経路として指定できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>（例外支給）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>第7条　会社が必要と判断した場合には、前条の基準を超えて通勤手当を支給することがある。その場合、当該支給額は課税対象となる可能性があることを従業員は承知するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="8" customHeight="1"/>
+    <row r="83" ht="8" customHeight="1">
+      <c r="A83" s="28" t="inlineStr"/>
+      <c r="B83" s="12" t="n"/>
+      <c r="C83" s="12" t="n"/>
+      <c r="D83" s="12" t="n"/>
+      <c r="E83" s="12" t="n"/>
+    </row>
+    <row r="84" ht="10" customHeight="1"/>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>第4章　特別通勤手当</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
+          <t>（支給対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>第8条　会社は、従業員が通勤のために負担した駐輪場利用料等について、次のとおり特別通勤手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>1　駐輪場の月極契約金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>2　一時利用料 × 出勤日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>3　その他事前申請の上会社が合理的と認めるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="8" customHeight="1"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>（支給限度額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>第9条　特別通勤手当の上限は月額10,000円とする。超過分は従業員負担とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="8" customHeight="1"/>
+    <row r="95" ht="8" customHeight="1">
+      <c r="A95" s="28" t="inlineStr"/>
+      <c r="B95" s="12" t="n"/>
+      <c r="C95" s="12" t="n"/>
+      <c r="D95" s="12" t="n"/>
+      <c r="E95" s="12" t="n"/>
+    </row>
+    <row r="96" ht="10" customHeight="1"/>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="25" t="inlineStr">
+        <is>
+          <t>第5章　住宅手当</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="26" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>第10条　本手当に関する用語の定義は、次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>1　「社員」とは、会社に雇用される全ての正社員をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>2　「賃料」とは、賃貸借契約書に記載された月額家賃をいい、共益費・管理費・水道光熱費等の付帯費用は含まないものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="27" t="inlineStr">
+        <is>
+          <t>3　「対象住宅」とは、社員が自己名義または同居配偶者名義の賃貸住宅に居住するものをいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="26" t="inlineStr">
+        <is>
+          <t>（支給対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>第11条　本手当の支給対象者は、第10条に定義する対象住宅に居住し、本規程に定める申請手続きを完了した社員とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
+          <t>2　配偶者等が他の会社から住宅手当を受給している場合、当該社員は本手当の支給対象外とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>（支給要件・申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>第12条　住宅手当を受給しようとする社員は、次の書類をマネジメント本部長宛てに提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>1　住宅手当申請書兼誓約書（賃料、配偶者等が他社から住宅手当を受給していないことの念書を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>2　賃貸借契約書の写し（賃料確認用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>3　同居家族構成届（氏名、続柄、生年月日、同居・別居区分を明記）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>4　世帯主証明書（住民票の写し等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>2　同月中に申請がない場合は当該月分の支給を受けられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>3　賃料が減少した場合は、遅滞なくマネジメント本部へ変更届を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="8" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>（支給額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>第13条　住宅手当額は、賃料（月額）×30％の金額を算出し、100円未満を切り上げた額とする。ただし、支給額が30,000円を超える場合は30,000円を上限とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="26" t="inlineStr">
+        <is>
+          <t>（変更届出義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>第14条　住宅手当に関わる以下の事項に変更が生じた場合、社員は速やかにマネジメント本部へ届出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>1　賃料額の増減</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>2　住居の転居または同居家族構成の変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="8" customHeight="1"/>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="26" t="inlineStr">
+        <is>
+          <t>（不正受給時の措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="32" customHeight="1">
+      <c r="A126" s="27" t="inlineStr">
+        <is>
+          <t>第15条　虚偽の申請または書類偽造等により住宅手当を受給した場合、会社は既に支給した住宅手当の全額返還を命じるとともに、懲戒規程に基づき処分を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="8" customHeight="1"/>
+    <row r="128" ht="8" customHeight="1">
+      <c r="A128" s="28" t="inlineStr"/>
+      <c r="B128" s="12" t="n"/>
+      <c r="C128" s="12" t="n"/>
+      <c r="D128" s="12" t="n"/>
+      <c r="E128" s="12" t="n"/>
+    </row>
+    <row r="129" ht="10" customHeight="1"/>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="25" t="inlineStr">
+        <is>
+          <t>第6章　生活支援・慶弔関係</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="26" t="inlineStr">
+        <is>
+          <t>（食事補助手当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="27" t="inlineStr">
+        <is>
+          <t>第16条　会社は、正社員に対し、一律月額10,000円の食事補助手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="8" customHeight="1"/>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="26" t="inlineStr">
+        <is>
+          <t>（制服・作業着）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="32" customHeight="1">
+      <c r="A135" s="27" t="inlineStr">
+        <is>
+          <t>第17条　従業員は、業務に従事するにあたり会社が指定する制服または作業着を着用しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="32" customHeight="1">
+      <c r="A136" s="27" t="inlineStr">
+        <is>
+          <t>2　制服または作業着は、原則として従業員が自ら準備するものとする。ただし、会社が特に必要と認めた場合は、会社が貸与または支給することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="8" customHeight="1"/>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="26" t="inlineStr">
+        <is>
+          <t>（慶弔給付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="27" t="inlineStr">
+        <is>
+          <t>第18条　会社は、休暇規程に定める慶弔休暇に関連して、次の給付を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="27" t="inlineStr">
+        <is>
+          <t>1　結婚祝い金：30,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="27" t="inlineStr">
+        <is>
+          <t>2　出産祝い金：30,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="27" t="inlineStr">
+        <is>
+          <t>3　弔事：本人または家族の希望に応じ、生花を手配する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="27" t="inlineStr">
+        <is>
+          <t>4　災害見舞金：取締役会の判断により、最大100,000円を限度として支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="8" customHeight="1"/>
+    <row r="145" ht="8" customHeight="1">
+      <c r="A145" s="28" t="inlineStr"/>
+      <c r="B145" s="12" t="n"/>
+      <c r="C145" s="12" t="n"/>
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="12" t="n"/>
+    </row>
+    <row r="146" ht="10" customHeight="1"/>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="25" t="inlineStr">
+        <is>
+          <t>第7章　健康・医療支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="26" t="inlineStr">
+        <is>
+          <t>（健康診断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="32" customHeight="1">
+      <c r="A149" s="27" t="inlineStr">
+        <is>
+          <t>第19条　会社は、労働安全衛生法に基づき、従業員に対し年1回の健康診断を実施し、費用を会社が負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="27" t="inlineStr">
+        <is>
+          <t>2　夜勤に従事する従業員については、年2回実施し、費用は会社が負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="8" customHeight="1"/>
+    <row r="152" ht="8" customHeight="1">
+      <c r="A152" s="28" t="inlineStr"/>
+      <c r="B152" s="12" t="n"/>
+      <c r="C152" s="12" t="n"/>
+      <c r="D152" s="12" t="n"/>
+      <c r="E152" s="12" t="n"/>
+    </row>
+    <row r="153" ht="10" customHeight="1"/>
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="25" t="inlineStr">
+        <is>
+          <t>第8章　教育研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="26" t="inlineStr">
+        <is>
+          <t>（外部研修）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="27" t="inlineStr">
+        <is>
+          <t>第20条　会社は、業務に資すると判断される外部研修について、参加費用を全額負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="8" customHeight="1"/>
+    <row r="158" ht="8" customHeight="1">
+      <c r="A158" s="28" t="inlineStr"/>
+      <c r="B158" s="12" t="n"/>
+      <c r="C158" s="12" t="n"/>
+      <c r="D158" s="12" t="n"/>
+      <c r="E158" s="12" t="n"/>
+    </row>
+    <row r="159" ht="10" customHeight="1"/>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="25" t="inlineStr">
+        <is>
+          <t>第9章　特別休暇に関連する給付</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="26" t="inlineStr">
+        <is>
+          <t>（誕生日休暇・手当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="32" customHeight="1">
+      <c r="A162" s="27" t="inlineStr">
+        <is>
+          <t>第21条　会社は、休暇規程に基づき誕生日休暇を付与するとともに、当該休暇を取得した従業員に対して誕生日手当として10,000円を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="8" customHeight="1"/>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="26" t="inlineStr">
+        <is>
+          <t>（特別休暇に伴う給付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="32" customHeight="1">
+      <c r="A165" s="27" t="inlineStr">
+        <is>
+          <t>第22条　会社は、休暇規程に基づき付与される特別休暇について、必要に応じて記念品、金銭その他の給付を行うことができる。内容は取締役会の決議により定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="8" customHeight="1"/>
+    <row r="167" ht="8" customHeight="1">
+      <c r="A167" s="28" t="inlineStr"/>
+      <c r="B167" s="12" t="n"/>
+      <c r="C167" s="12" t="n"/>
+      <c r="D167" s="12" t="n"/>
+      <c r="E167" s="12" t="n"/>
+    </row>
+    <row r="168" ht="10" customHeight="1"/>
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="25" t="inlineStr">
+        <is>
+          <t>第10章　運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="26" t="inlineStr">
+        <is>
+          <t>（支給方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="32" customHeight="1">
+      <c r="A171" s="27" t="inlineStr">
+        <is>
+          <t>第23条　通勤手当、特別通勤手当及び各種手当は、毎月1日から末日までの1か月分を集計し、当月の給与と併せて支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="8" customHeight="1"/>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="26" t="inlineStr">
+        <is>
+          <t>（中途入社・退職時の取扱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="27" t="inlineStr">
+        <is>
+          <t>第24条　月中に入社または退職した者についても、出勤日数に応じて日割り計算で支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="8" customHeight="1"/>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="26" t="inlineStr">
+        <is>
+          <t>（休職・休暇・在宅勤務時の取扱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="32" customHeight="1">
+      <c r="A177" s="27" t="inlineStr">
+        <is>
+          <t>第25条　休職中・休暇中・休業中または在宅勤務の場合、通勤手当及び特別通勤手当は支給しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="8" customHeight="1"/>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="26" t="inlineStr">
+        <is>
+          <t>（虚偽申請の禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="27" t="inlineStr">
+        <is>
+          <t>第26条　通勤手当、特別通勤手当、住宅手当その他各種手当の申請に虚偽が発覚した場合、会社は入社時に遡って再計算を行い、超過支給分を返還請求できるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="8" customHeight="1"/>
+    <row r="182" ht="8" customHeight="1">
+      <c r="A182" s="28" t="inlineStr"/>
+      <c r="B182" s="12" t="n"/>
+      <c r="C182" s="12" t="n"/>
+      <c r="D182" s="12" t="n"/>
+      <c r="E182" s="12" t="n"/>
+    </row>
+    <row r="183" ht="10" customHeight="1"/>
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="25" t="inlineStr">
+        <is>
+          <t>第11章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="26" t="inlineStr">
+        <is>
+          <t>（周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="32" customHeight="1">
+      <c r="A186" s="27" t="inlineStr">
+        <is>
+          <t>第27条　会社は、本規程の内容を従業員に周知し、常時確認できるよう掲示またはイントラネット等で公開する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="8" customHeight="1"/>
+    <row r="188" ht="8" customHeight="1">
+      <c r="A188" s="28" t="inlineStr"/>
+      <c r="B188" s="12" t="n"/>
+      <c r="C188" s="12" t="n"/>
+      <c r="D188" s="12" t="n"/>
+      <c r="E188" s="12" t="n"/>
+    </row>
+    <row r="189" ht="10" customHeight="1"/>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="121">
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A182:E182"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A192:E192"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A179:E179"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A185:E185"/>
+    <mergeCell ref="A184:E184"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A171:E171"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A173:E173"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A161:E161"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A186:E186"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A174:E174"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A160:E160"/>
+    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A191:E191"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A162:E162"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A164:E164"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A154:E154"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A188:E188"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A180:E180"/>
+    <mergeCell ref="A190:E190"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A143:E143"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　福利厚生規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4745,6 +4746,417 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>競業避止規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の事業上の正当な利益を保護し、従業員による競業行為を防止するとともに、従業員の職業選択の自由との調和を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用される従業員のうち、経営管理、営業、研究開発その他会社が特に指定する者に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>2　派遣社員、業務委託契約者等については、個別契約に基づき適用することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>第3条　本規程における「競業行為」とは、会社と同一または類似の事業を営む行為、会社と競合する他社への就業、または会社の取引先を利用して自己または第三者の利益を図る行為をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="8" customHeight="1">
+      <c r="A37" s="28" t="inlineStr"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="10" customHeight="1"/>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>第2章　在職中の義務</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>（競業禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>第4条　従業員は、在職中、会社の承認なく競業行為を行ってはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>（副業・兼業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>第5条　従業員は、副業・兼業を行う場合であっても、会社の業務に支障を及ぼさず、かつ競業行為に該当しない範囲に限り許可される。詳細は「人事管理規程」及び「副業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="8" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>（秘密情報の利用禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>第6条　従業員は、在職中に知り得た会社の秘密情報を利用して競業行為を行ってはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="8" customHeight="1">
+      <c r="A49" s="28" t="inlineStr"/>
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+    </row>
+    <row r="50" ht="10" customHeight="1"/>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>第3章　退職後の義務</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t>（競業避止義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>第7条　管理職、営業担当その他会社が特に指定した従業員は、退職後1年間、会社が営業する地域（大阪府・兵庫県・京都府・奈良県）において、会社と競合する事業に従事してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>（合理的範囲の限定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>第8条　前条の地域・期間は、会社の事業規模、従業員の職務内容、社会通念を考慮し、合理的な範囲に限定される。過度に広範な競業禁止は適用しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>（補償）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>第9条　会社は、退職後競業避止義務を個別合意で課す場合、社会通念上相当と認められる補償を行う。補償の内容は合意時に明示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
+    <row r="61" ht="8" customHeight="1">
+      <c r="A61" s="28" t="inlineStr"/>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+    </row>
+    <row r="62" ht="10" customHeight="1"/>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>第4章　管理・措置</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="26" t="inlineStr">
+        <is>
+          <t>（特別合意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>第10条　会社は、必要に応じ、従業員との間で退職後競業避止に関する特別合意を締結することができる。その場合、地域、期間、業務範囲及び補償内容を明示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>（違反時の措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>第11条　従業員が在職中に本規程に違反した場合は「懲戒規程」に基づき懲戒処分の対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>2　従業員が退職後に本規程に違反し会社に損害を与えた場合は、会社は法令に基づき損害賠償を請求することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="8" customHeight="1">
+      <c r="A71" s="28" t="inlineStr"/>
+      <c r="B71" s="12" t="n"/>
+      <c r="C71" s="12" t="n"/>
+      <c r="D71" s="12" t="n"/>
+      <c r="E71" s="12" t="n"/>
+    </row>
+    <row r="72" ht="10" customHeight="1"/>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>第5章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="26" t="inlineStr">
+        <is>
+          <t>（他規程との関係）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>第12条　本規程に定めのない事項は、就業規則、情報管理規程、秘密保持契約その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="8" customHeight="1">
+      <c r="A77" s="28" t="inlineStr"/>
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="12" t="n"/>
+      <c r="D77" s="12" t="n"/>
+      <c r="E77" s="12" t="n"/>
+    </row>
+    <row r="78" ht="10" customHeight="1"/>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程施行前に締結された労働契約その他の合意についても、本規程に反しない範囲で適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="42">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　競業避止規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5157,6 +5158,575 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>育児・介護休業規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員が、育児・介護休業法その他関係法令に基づき、仕事と育児・介護を両立できるよう育児休業、介護休業等の制度を定め、従業員の職業生活の安定と充実を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用される全ての正社員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>2　契約社員、嘱託社員、パートタイマー等については、労働契約書において別段の定めがある場合を除き、本規程を準用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>第3条　本規程における用語の定義は、育児・介護休業法に準拠し、次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>1　「育児休業」：満1歳に満たない子を養育するために取得する休業をいう。ただし、一定の場合は1歳6か月、さらに2歳まで延長できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>2　「介護休業」：要介護状態にある家族（法令に定める範囲）を介護するために取得する休業をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>3　「子の看護休暇」：小学校就学前の子の看護のために取得できる休暇をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>4　「介護休暇」：要介護状態にある家族の介護や通院付添のために取得できる休暇をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="8" customHeight="1"/>
+    <row r="41" ht="8" customHeight="1">
+      <c r="A41" s="28" t="inlineStr"/>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="10" customHeight="1"/>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>第2章　育児休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>（育児休業の取得要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>第4条　従業員は、1歳に満たない子を養育する場合、会社に申し出ることにより育児休業を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>2　配偶者が常態として子を養育できる場合等、法令で育児休業が認められない場合は除く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>（育児休業の期間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>第5条　育児休業の期間は、原則として子が1歳に達するまでとする。ただし、保育所に入所できない場合等、法令の定めに従い1歳6か月、最長2歳まで延長できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>（育児休業の申出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>第6条　育児休業を取得しようとする従業員は、原則として休業開始予定日の1か月前までに、所定の書式により会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>（育児休業中の処遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>第7条　育児休業中は無給とする。ただし、雇用保険法に基づき育児休業給付金の受給が可能である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>2　社会保険料の免除については、健康保険法及び厚生年金保険法の定めに従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="8" customHeight="1">
+      <c r="A58" s="28" t="inlineStr"/>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+    </row>
+    <row r="59" ht="10" customHeight="1"/>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>第3章　介護休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>（介護休業の取得要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>第8条　従業員は、要介護状態にある家族を介護する場合、会社に申し出ることにより介護休業を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="8" customHeight="1"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="26" t="inlineStr">
+        <is>
+          <t>（介護休業の期間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>第9条　介護休業は、対象家族1人につき通算93日まで取得できる。分割して3回まで分けて取得することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>（介護休業の申出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>第10条　介護休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに、所定の書式により会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="8" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="26" t="inlineStr">
+        <is>
+          <t>（介護休業中の処遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>第11条　介護休業中は無給とする。ただし、雇用保険法に基づき介護休業給付金の受給が可能である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="8" customHeight="1">
+      <c r="A73" s="28" t="inlineStr"/>
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="12" t="n"/>
+      <c r="D73" s="12" t="n"/>
+      <c r="E73" s="12" t="n"/>
+    </row>
+    <row r="74" ht="10" customHeight="1"/>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>第4章　子の看護休暇・介護休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
+          <t>（子の看護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、小学校就学前の子が病気やけがをした場合、看護のため年5日（子が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>2　子の看護休暇は、1日または半日単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>（介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、要介護状態にある家族の介護や通院付添のため、年5日（対象家族が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>2　介護休暇は、1日または半日単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="8" customHeight="1">
+      <c r="A84" s="28" t="inlineStr"/>
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="12" t="n"/>
+      <c r="D84" s="12" t="n"/>
+      <c r="E84" s="12" t="n"/>
+    </row>
+    <row r="85" ht="10" customHeight="1"/>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="25" t="inlineStr">
+        <is>
+          <t>第5章　復職・不利益取扱い禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>（復職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>第14条　育児休業または介護休業を終了した従業員は、原則として休業前と同じ職務に復職させる。ただし、業務運営上やむを得ない場合は、同等の地位・待遇を有する職務に配置することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>第15条　会社は、従業員が育児休業・介護休業・子の看護休暇・介護休暇を取得したことを理由として、解雇その他不利益な取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="8" customHeight="1">
+      <c r="A93" s="28" t="inlineStr"/>
+      <c r="B93" s="12" t="n"/>
+      <c r="C93" s="12" t="n"/>
+      <c r="D93" s="12" t="n"/>
+      <c r="E93" s="12" t="n"/>
+    </row>
+    <row r="94" ht="10" customHeight="1"/>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="25" t="inlineStr">
+        <is>
+          <t>第6章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="26" t="inlineStr">
+        <is>
+          <t>（制度の周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>第16条　会社は、本規程の内容を就業規則とともに従業員へ周知し、希望者が適切に制度を利用できるよう努めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="26" t="inlineStr">
+        <is>
+          <t>（個人情報保護）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、休業申請や取得に関して知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="8" customHeight="1"/>
+    <row r="102" ht="8" customHeight="1">
+      <c r="A102" s="28" t="inlineStr"/>
+      <c r="B102" s="12" t="n"/>
+      <c r="C102" s="12" t="n"/>
+      <c r="D102" s="12" t="n"/>
+      <c r="E102" s="12" t="n"/>
+    </row>
+    <row r="103" ht="10" customHeight="1"/>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、育児・介護休業法、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="61">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　育児・介護休業規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -19,7 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -213,6 +214,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -5727,6 +5734,658 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E105"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>退職規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における従業員の退職に関する手続及び退職金制度を定め、円滑な人事管理、公正な取扱い及び適正な労務運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、役員については別途定めるところによる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>第3条　本規程において「退職」とは、従業員が会社との雇用契約を終了することをいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>2　「退職金」とは、本規程に基づき会社が従業員に支給する金銭をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="8" customHeight="1">
+      <c r="A37" s="28" t="inlineStr"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="10" customHeight="1"/>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>第2章　退職の手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>（退職の種類）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>第4条　退職は、次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>1　定年退職</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>2　自己都合退職</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>3　会社都合退職（整理解雇、事業所閉鎖、業務縮小等を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>4　自然退職（死亡、契約期間満了、行方不明 等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>（退職の申出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>第5条　従業員が自己都合により退職を希望する場合は、原則として退職希望日の30日前までに所定の退職届を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="8" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>（引継ぎ義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>第6条　退職する従業員は、会社が指定する業務の引継ぎを誠実に行い、職務上の責任を果たさなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>（会社物品の返還）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>第7条　退職する従業員は、退職日までに会社から貸与された備品、制服、身分証、書類、電子機器その他の物品を返還しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="8" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>（退職証明書の交付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>第8条　従業員が退職した場合、本人の請求に基づき、労働基準法第22条に定める退職証明書を交付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="8" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>（賃金の精算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>第9条　退職に際しては、労働基準法第23条に基づき、未払賃金その他の金銭を退職日から7日以内に支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t>（秘密保持義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>第10条　退職した従業員は、在職中に知り得た会社の営業秘密、顧客情報、個人情報その他の秘密を退職後も漏洩してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="8" customHeight="1">
+      <c r="A65" s="28" t="inlineStr"/>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+    </row>
+    <row r="66" ht="10" customHeight="1"/>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>第3章　退職金</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="26" t="inlineStr">
+        <is>
+          <t>（支給対象者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>第11条　勤続1年以上の従業員が退職した場合、会社は退職金を支給する。ただし、第15条に定める不支給事由に該当する場合は支給しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="26" t="inlineStr">
+        <is>
+          <t>（勤続年数の算定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>第12条　勤続年数は、入社日から退職日までの期間により算定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>2　1年未満の端数については次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　6か月未満の端数は切り捨てる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　6か月以上の端数は1年に切り上げる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>（退職金の算定方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>第13条　退職金の額は、次の算式により算定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>退職金 ＝ 退職時基本給 × 支給係数 × 勤続年数</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>（支給係数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>第14条　支給係数は、勤続年数及び退職理由に応じて次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>勤続年数</t>
+        </is>
+      </c>
+      <c r="B83" s="33" t="inlineStr">
+        <is>
+          <t>自己都合</t>
+        </is>
+      </c>
+      <c r="C83" s="33" t="inlineStr">
+        <is>
+          <t>会社都合</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>1年以上3年未満</t>
+        </is>
+      </c>
+      <c r="B84" s="34" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="C84" s="34" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
+          <t>3年以上6年未満</t>
+        </is>
+      </c>
+      <c r="B85" s="34" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="C85" s="34" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>6年以上9年未満</t>
+        </is>
+      </c>
+      <c r="B86" s="34" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C86" s="34" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>9年以上15年未満</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="C87" s="34" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>15年以上25年未満</t>
+        </is>
+      </c>
+      <c r="B88" s="34" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="C88" s="34" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
+          <t>25年以上</t>
+        </is>
+      </c>
+      <c r="B89" s="34" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="C89" s="34" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="8" customHeight="1"/>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="26" t="inlineStr">
+        <is>
+          <t>（不支給事由）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>第15条　従業員が次の各号のいずれかに該当する場合は、退職金を支給しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>1　懲戒解雇された場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>2　重大な背信行為により会社に著しい損害を与えた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>3　虚偽の申告により雇用契約を締結したことが判明した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>（支給手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>第16条　退職金は、退職日から2か月以内に本人の指定口座に振り込む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>2　会社は必要に応じて退職金の一部または全部を分割して支給することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="8" customHeight="1"/>
+    <row r="101" ht="8" customHeight="1">
+      <c r="A101" s="28" t="inlineStr"/>
+      <c r="B101" s="12" t="n"/>
+      <c r="C101" s="12" t="n"/>
+      <c r="D101" s="12" t="n"/>
+      <c r="E101" s="12" t="n"/>
+    </row>
+    <row r="102" ht="10" customHeight="1"/>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="57">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　退職規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>
@@ -5737,96 +6396,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="35" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>法人名</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>ええかいご → いいかいご（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>管理者・サービス提供責任者等</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>要入力</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>なし（すべて入力済み）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>コメント付きセル</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>説明年月日・利用者欄</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>新しく使えるよう空欄にしています</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>元の資料</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
         </is>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -2028,7 +2028,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="750" customHeight="1">
+    <row r="103" ht="120" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
           <t>介護職員等処遇改善加算
@@ -2041,21 +2041,7 @@
           <t>（Ⅰ）所定単位数の245/1000
 （Ⅱ）所定単位数の224/1000
 （Ⅲ）所定単位数の182/1000
-（Ⅳ）所定単位数の145/1000
-（Ⅴ1）所定単位数の221/1000
-（Ⅴ2）所定単位数の208/1000
-（Ⅴ3）所定単位数の200/1000
-（Ⅴ4）所定単位数の187/1000
-（Ⅴ5）所定単位数の184/1000
-（Ⅴ6）所定単位数の163/1000
-（Ⅴ7）所定単位数の163/1000
-（Ⅴ8）所定単位数の158/1000
-（Ⅴ9）所定単位数の142/1000
-（Ⅴ10）所定単位数の139/1000
-（Ⅴ11）所定単位数の121/1000
-（Ⅴ12）所定単位数の118/1000
-（Ⅴ13）所定単位数の100/1000
-（Ⅴ14）所定単位数の76/1000</t>
+（Ⅳ）所定単位数の145/1000</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -2065,8 +2051,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>基本サービス費に各種加算減算を加えた総単位数（所定単位数）
-※（Ⅴ）は令和7年3月31日まで算定可</t>
+          <t>基本サービス費に各種加算減算を加えた総単位数（所定単位数）</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2320,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>１提供当たりの料金の100%を請求いたします。</t>
+          <t>１提供当たりの利用者負担額の50%を請求いたします。</t>
         </is>
       </c>
       <c r="D141" s="4" t="n"/>
@@ -2354,7 +2339,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>１提供当たりの料金の50%を請求いたします。</t>
+          <t>１提供当たりの利用者負担額の100%を請求いたします。</t>
         </is>
       </c>
       <c r="D142" s="4" t="n"/>
@@ -3593,7 +3578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4293,331 +4278,341 @@
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="27" t="inlineStr">
         <is>
-          <t>第16条　会社は、正社員に対し、一律月額10,000円の食事補助手当を支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="8" customHeight="1"/>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="26" t="inlineStr">
+          <t>第16条　会社は、従業員に対し、月額10,000円の食事補助手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" s="27" t="inlineStr">
+        <is>
+          <t>2　パートタイマー等の所定労働日数が少ない従業員については、出勤日数に応じて按分して支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="8" customHeight="1"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="26" t="inlineStr">
         <is>
           <t>（制服・作業着）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="32" customHeight="1">
-      <c r="A135" s="27" t="inlineStr">
-        <is>
-          <t>第17条　従業員は、業務に従事するにあたり会社が指定する制服または作業着を着用しなければならない。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="32" customHeight="1">
       <c r="A136" s="27" t="inlineStr">
         <is>
+          <t>第17条　従業員は、業務に従事するにあたり会社が指定する制服または作業着を着用しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
           <t>2　制服または作業着は、原則として従業員が自ら準備するものとする。ただし、会社が特に必要と認めた場合は、会社が貸与または支給することがある。</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="8" customHeight="1"/>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="26" t="inlineStr">
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="26" t="inlineStr">
         <is>
           <t>（慶弔給付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="27" t="inlineStr">
-        <is>
-          <t>第18条　会社は、休暇規程に定める慶弔休暇に関連して、次の給付を行う。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="27" t="inlineStr">
         <is>
-          <t>1　結婚祝い金：30,000円</t>
+          <t>第18条　会社は、休暇規程に定める慶弔休暇に関連して、次の給付を行う。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="27" t="inlineStr">
         <is>
-          <t>2　出産祝い金：30,000円</t>
+          <t>1　結婚祝い金：30,000円</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="27" t="inlineStr">
         <is>
-          <t>3　弔事：本人または家族の希望に応じ、生花を手配する。</t>
+          <t>2　出産祝い金：30,000円</t>
         </is>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="27" t="inlineStr">
         <is>
+          <t>3　弔事：本人または家族の希望に応じ、生花を手配する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="27" t="inlineStr">
+        <is>
           <t>4　災害見舞金：取締役会の判断により、最大100,000円を限度として支給する。</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="8" customHeight="1"/>
-    <row r="145" ht="8" customHeight="1">
-      <c r="A145" s="28" t="inlineStr"/>
-      <c r="B145" s="12" t="n"/>
-      <c r="C145" s="12" t="n"/>
-      <c r="D145" s="12" t="n"/>
-      <c r="E145" s="12" t="n"/>
-    </row>
-    <row r="146" ht="10" customHeight="1"/>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="25" t="inlineStr">
+    <row r="145" ht="8" customHeight="1"/>
+    <row r="146" ht="8" customHeight="1">
+      <c r="A146" s="28" t="inlineStr"/>
+      <c r="B146" s="12" t="n"/>
+      <c r="C146" s="12" t="n"/>
+      <c r="D146" s="12" t="n"/>
+      <c r="E146" s="12" t="n"/>
+    </row>
+    <row r="147" ht="10" customHeight="1"/>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="25" t="inlineStr">
         <is>
           <t>第7章　健康・医療支援</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="26" t="inlineStr">
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="26" t="inlineStr">
         <is>
           <t>（健康診断）</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="32" customHeight="1">
-      <c r="A149" s="27" t="inlineStr">
+    <row r="150" ht="32" customHeight="1">
+      <c r="A150" s="27" t="inlineStr">
         <is>
           <t>第19条　会社は、労働安全衛生法に基づき、従業員に対し年1回の健康診断を実施し、費用を会社が負担する。</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="27" t="inlineStr">
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="27" t="inlineStr">
         <is>
           <t>2　夜勤に従事する従業員については、年2回実施し、費用は会社が負担する。</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="8" customHeight="1"/>
-    <row r="152" ht="8" customHeight="1">
-      <c r="A152" s="28" t="inlineStr"/>
-      <c r="B152" s="12" t="n"/>
-      <c r="C152" s="12" t="n"/>
-      <c r="D152" s="12" t="n"/>
-      <c r="E152" s="12" t="n"/>
-    </row>
-    <row r="153" ht="10" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1">
-      <c r="A154" s="25" t="inlineStr">
+    <row r="152" ht="8" customHeight="1"/>
+    <row r="153" ht="8" customHeight="1">
+      <c r="A153" s="28" t="inlineStr"/>
+      <c r="B153" s="12" t="n"/>
+      <c r="C153" s="12" t="n"/>
+      <c r="D153" s="12" t="n"/>
+      <c r="E153" s="12" t="n"/>
+    </row>
+    <row r="154" ht="10" customHeight="1"/>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="25" t="inlineStr">
         <is>
           <t>第8章　教育研修</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="26" t="inlineStr">
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="26" t="inlineStr">
         <is>
           <t>（外部研修）</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="27" t="inlineStr">
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="27" t="inlineStr">
         <is>
           <t>第20条　会社は、業務に資すると判断される外部研修について、参加費用を全額負担する。</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="8" customHeight="1"/>
-    <row r="158" ht="8" customHeight="1">
-      <c r="A158" s="28" t="inlineStr"/>
-      <c r="B158" s="12" t="n"/>
-      <c r="C158" s="12" t="n"/>
-      <c r="D158" s="12" t="n"/>
-      <c r="E158" s="12" t="n"/>
-    </row>
-    <row r="159" ht="10" customHeight="1"/>
-    <row r="160" ht="30" customHeight="1">
-      <c r="A160" s="25" t="inlineStr">
+    <row r="158" ht="8" customHeight="1"/>
+    <row r="159" ht="8" customHeight="1">
+      <c r="A159" s="28" t="inlineStr"/>
+      <c r="B159" s="12" t="n"/>
+      <c r="C159" s="12" t="n"/>
+      <c r="D159" s="12" t="n"/>
+      <c r="E159" s="12" t="n"/>
+    </row>
+    <row r="160" ht="10" customHeight="1"/>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="25" t="inlineStr">
         <is>
           <t>第9章　特別休暇に関連する給付</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="26" t="inlineStr">
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="26" t="inlineStr">
         <is>
           <t>（誕生日休暇・手当）</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="27" t="inlineStr">
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="27" t="inlineStr">
         <is>
           <t>第21条　会社は、休暇規程に基づき誕生日休暇を付与するとともに、当該休暇を取得した従業員に対して誕生日手当として10,000円を支給する。</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="8" customHeight="1"/>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="26" t="inlineStr">
+    <row r="164" ht="8" customHeight="1"/>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="26" t="inlineStr">
         <is>
           <t>（特別休暇に伴う給付）</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="32" customHeight="1">
-      <c r="A165" s="27" t="inlineStr">
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="27" t="inlineStr">
         <is>
           <t>第22条　会社は、休暇規程に基づき付与される特別休暇について、必要に応じて記念品、金銭その他の給付を行うことができる。内容は取締役会の決議により定める。</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="8" customHeight="1"/>
-    <row r="167" ht="8" customHeight="1">
-      <c r="A167" s="28" t="inlineStr"/>
-      <c r="B167" s="12" t="n"/>
-      <c r="C167" s="12" t="n"/>
-      <c r="D167" s="12" t="n"/>
-      <c r="E167" s="12" t="n"/>
-    </row>
-    <row r="168" ht="10" customHeight="1"/>
-    <row r="169" ht="30" customHeight="1">
-      <c r="A169" s="25" t="inlineStr">
+    <row r="167" ht="8" customHeight="1"/>
+    <row r="168" ht="8" customHeight="1">
+      <c r="A168" s="28" t="inlineStr"/>
+      <c r="B168" s="12" t="n"/>
+      <c r="C168" s="12" t="n"/>
+      <c r="D168" s="12" t="n"/>
+      <c r="E168" s="12" t="n"/>
+    </row>
+    <row r="169" ht="10" customHeight="1"/>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="25" t="inlineStr">
         <is>
           <t>第10章　運用</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="26" t="inlineStr">
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="26" t="inlineStr">
         <is>
           <t>（支給方法）</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="32" customHeight="1">
-      <c r="A171" s="27" t="inlineStr">
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="27" t="inlineStr">
         <is>
           <t>第23条　通勤手当、特別通勤手当及び各種手当は、毎月1日から末日までの1か月分を集計し、当月の給与と併せて支給する。</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="8" customHeight="1"/>
-    <row r="173" ht="20" customHeight="1">
-      <c r="A173" s="26" t="inlineStr">
+    <row r="173" ht="8" customHeight="1"/>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="26" t="inlineStr">
         <is>
           <t>（中途入社・退職時の取扱い）</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="27" t="inlineStr">
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="27" t="inlineStr">
         <is>
           <t>第24条　月中に入社または退職した者についても、出勤日数に応じて日割り計算で支給する。</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="8" customHeight="1"/>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="26" t="inlineStr">
+    <row r="176" ht="8" customHeight="1"/>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="26" t="inlineStr">
         <is>
           <t>（休職・休暇・在宅勤務時の取扱い）</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="32" customHeight="1">
-      <c r="A177" s="27" t="inlineStr">
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" s="27" t="inlineStr">
         <is>
           <t>第25条　休職中・休暇中・休業中または在宅勤務の場合、通勤手当及び特別通勤手当は支給しない。</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="8" customHeight="1"/>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="26" t="inlineStr">
+    <row r="179" ht="8" customHeight="1"/>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="26" t="inlineStr">
         <is>
           <t>（虚偽申請の禁止）</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="27" t="inlineStr">
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="27" t="inlineStr">
         <is>
           <t>第26条　通勤手当、特別通勤手当、住宅手当その他各種手当の申請に虚偽が発覚した場合、会社は入社時に遡って再計算を行い、超過支給分を返還請求できるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="8" customHeight="1"/>
-    <row r="182" ht="8" customHeight="1">
-      <c r="A182" s="28" t="inlineStr"/>
-      <c r="B182" s="12" t="n"/>
-      <c r="C182" s="12" t="n"/>
-      <c r="D182" s="12" t="n"/>
-      <c r="E182" s="12" t="n"/>
-    </row>
-    <row r="183" ht="10" customHeight="1"/>
-    <row r="184" ht="30" customHeight="1">
-      <c r="A184" s="25" t="inlineStr">
+    <row r="182" ht="8" customHeight="1"/>
+    <row r="183" ht="8" customHeight="1">
+      <c r="A183" s="28" t="inlineStr"/>
+      <c r="B183" s="12" t="n"/>
+      <c r="C183" s="12" t="n"/>
+      <c r="D183" s="12" t="n"/>
+      <c r="E183" s="12" t="n"/>
+    </row>
+    <row r="184" ht="10" customHeight="1"/>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="25" t="inlineStr">
         <is>
           <t>第11章　雑則</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="20" customHeight="1">
-      <c r="A185" s="26" t="inlineStr">
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="26" t="inlineStr">
         <is>
           <t>（周知）</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="32" customHeight="1">
-      <c r="A186" s="27" t="inlineStr">
+    <row r="187" ht="32" customHeight="1">
+      <c r="A187" s="27" t="inlineStr">
         <is>
           <t>第27条　会社は、本規程の内容を従業員に周知し、常時確認できるよう掲示またはイントラネット等で公開する。</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="8" customHeight="1"/>
-    <row r="188" ht="8" customHeight="1">
-      <c r="A188" s="28" t="inlineStr"/>
-      <c r="B188" s="12" t="n"/>
-      <c r="C188" s="12" t="n"/>
-      <c r="D188" s="12" t="n"/>
-      <c r="E188" s="12" t="n"/>
-    </row>
-    <row r="189" ht="10" customHeight="1"/>
-    <row r="190" ht="30" customHeight="1">
-      <c r="A190" s="25" t="inlineStr">
+    <row r="188" ht="8" customHeight="1"/>
+    <row r="189" ht="8" customHeight="1">
+      <c r="A189" s="28" t="inlineStr"/>
+      <c r="B189" s="12" t="n"/>
+      <c r="C189" s="12" t="n"/>
+      <c r="D189" s="12" t="n"/>
+      <c r="E189" s="12" t="n"/>
+    </row>
+    <row r="190" ht="10" customHeight="1"/>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="25" t="inlineStr">
         <is>
           <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="20" customHeight="1">
-      <c r="A191" s="27" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
         </is>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="27" t="inlineStr">
         <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="27" t="inlineStr">
+        <is>
           <t>2　本規程は、令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="122">
+    <mergeCell ref="A166:E166"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A142:E142"/>
-    <mergeCell ref="A182:E182"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A168:E168"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A89:E89"/>
@@ -4628,10 +4623,9 @@
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
     <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A179:E179"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A185:E185"/>
-    <mergeCell ref="A184:E184"/>
+    <mergeCell ref="A181:E181"/>
     <mergeCell ref="A131:E131"/>
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A43:E43"/>
@@ -4642,29 +4636,31 @@
     <mergeCell ref="A115:E115"/>
     <mergeCell ref="A155:E155"/>
     <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A173:E173"/>
     <mergeCell ref="A130:E130"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A83:E83"/>
     <mergeCell ref="A148:E148"/>
-    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A157:E157"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A183:E183"/>
     <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A175:E175"/>
     <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A159:E159"/>
     <mergeCell ref="A97:E97"/>
     <mergeCell ref="A106:E106"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A147:E147"/>
     <mergeCell ref="A161:E161"/>
     <mergeCell ref="A170:E170"/>
     <mergeCell ref="A31:E31"/>
@@ -4674,59 +4670,56 @@
     <mergeCell ref="A73:E73"/>
     <mergeCell ref="A123:E123"/>
     <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A172:E172"/>
+    <mergeCell ref="A187:E187"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A174:E174"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A149:E149"/>
-    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="A189:E189"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A160:E160"/>
     <mergeCell ref="A141:E141"/>
     <mergeCell ref="A135:E135"/>
     <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A134:E134"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A152:E152"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A167:E167"/>
-    <mergeCell ref="A176:E176"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A98:E98"/>
     <mergeCell ref="A191:E191"/>
-    <mergeCell ref="A169:E169"/>
     <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A178:E178"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A153:E153"/>
     <mergeCell ref="A162:E162"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A177:E177"/>
     <mergeCell ref="A90:E90"/>
     <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A164:E164"/>
     <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A154:E154"/>
+    <mergeCell ref="A163:E163"/>
     <mergeCell ref="A101:E101"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A188:E188"/>
     <mergeCell ref="A126:E126"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A180:E180"/>
-    <mergeCell ref="A190:E190"/>
     <mergeCell ref="A102:E102"/>
     <mergeCell ref="A117:E117"/>
     <mergeCell ref="A111:E111"/>
@@ -5167,7 +5160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5292,69 +5285,75 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>3　「子の看護休暇」：小学校就学前の子の看護のために取得できる休暇をいう。</t>
+          <t>3　「子の看護等休暇」：小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のために取得できる休暇をいう。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="27" t="inlineStr">
         <is>
+          <t>5　「出生時育児休業」：子の出生後8週間以内に4週間（28日）まで取得できる休業をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
           <t>4　「介護休暇」：要介護状態にある家族の介護や通院付添のために取得できる休暇をいう。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="8" customHeight="1"/>
-    <row r="41" ht="8" customHeight="1">
-      <c r="A41" s="28" t="inlineStr"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="28" t="inlineStr"/>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="10" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>第2章　育児休業</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="26" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>（育児休業の取得要件）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="27" t="inlineStr">
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>第4条　従業員は、1歳に満たない子を養育する場合、会社に申し出ることにより育児休業を取得できる。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>2　配偶者が常態として子を養育できる場合等、法令で育児休業が認められない場合は除く。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>（育児休業の期間）</t>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>2　育児休業は、子1人につき原則2回まで分割して取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>3　労使協定により、次の者を育児休業の対象から除外することがある。（1）継続雇用期間が1年未満の者　（2）申出の日から1年以内に雇用関係が終了することが明らかな者　（3）1週間の所定労働日数が2日以下の者</t>
         </is>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>第5条　育児休業の期間は、原則として子が1歳に達するまでとする。ただし、保育所に入所できない場合等、法令の定めに従い1歳6か月、最長2歳まで延長できる。</t>
+          <t>4　有期雇用の従業員は、子が1歳6か月に達する日までに労働契約が満了し更新されないことが明らかでない場合に取得できる。</t>
         </is>
       </c>
     </row>
@@ -5362,14 +5361,14 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>（育児休業の申出）</t>
+          <t>（育児休業の期間）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>第6条　育児休業を取得しようとする従業員は、原則として休業開始予定日の1か月前までに、所定の書式により会社へ申し出なければならない。</t>
+          <t>第5条　育児休業の期間は、原則として子が1歳に達するまでとする。ただし、保育所に入所できない場合等、法令の定めに従い1歳6か月、最長2歳まで延長できる。</t>
         </is>
       </c>
     </row>
@@ -5377,341 +5376,527 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="26" t="inlineStr">
         <is>
-          <t>（育児休業中の処遇）</t>
+          <t>（育児休業の申出）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>第7条　育児休業中は無給とする。ただし、雇用保険法に基づき育児休業給付金の受給が可能である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>2　社会保険料の免除については、健康保険法及び厚生年金保険法の定めに従う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="8" customHeight="1"/>
-    <row r="58" ht="8" customHeight="1">
-      <c r="A58" s="28" t="inlineStr"/>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-    </row>
-    <row r="59" ht="10" customHeight="1"/>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>第3章　介護休業</t>
-        </is>
-      </c>
-    </row>
+          <t>第6条　育児休業を取得しようとする従業員は、原則として休業開始予定日の1か月前までに、所定の書式により会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>（出生時育児休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>第6条の2　従業員は、子の出生後8週間以内に、4週間（28日）を限度として、2回まで分割して出生時育児休業を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>2　出生時育児休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="26" t="inlineStr">
         <is>
-          <t>（介護休業の取得要件）</t>
+          <t>（育児休業中の処遇）</t>
         </is>
       </c>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="27" t="inlineStr">
         <is>
+          <t>第7条　育児休業中は無給とする。ただし、雇用保険法に基づき育児休業給付金の受給が可能である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>2　社会保険料の免除については、健康保険法及び厚生年金保険法の定めに従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="8" customHeight="1">
+      <c r="A65" s="28" t="inlineStr"/>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+    </row>
+    <row r="66" ht="10" customHeight="1"/>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>第3章　介護休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="26" t="inlineStr">
+        <is>
+          <t>（介護休業の取得要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
           <t>第8条　従業員は、要介護状態にある家族を介護する場合、会社に申し出ることにより介護休業を取得できる。</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="8" customHeight="1"/>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="26" t="inlineStr">
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="26" t="inlineStr">
         <is>
           <t>（介護休業の期間）</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="27" t="inlineStr">
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>第9条　介護休業は、対象家族1人につき通算93日まで取得できる。分割して3回まで分けて取得することができる。</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="8" customHeight="1"/>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="26" t="inlineStr">
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="26" t="inlineStr">
         <is>
           <t>（介護休業の申出）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="27" t="inlineStr">
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
         <is>
           <t>第10条　介護休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに、所定の書式により会社へ申し出なければならない。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="8" customHeight="1"/>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="26" t="inlineStr">
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>（介護休業中の処遇）</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="27" t="inlineStr">
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>第11条　介護休業中は無給とする。ただし、雇用保険法に基づき介護休業給付金の受給が可能である。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="8" customHeight="1"/>
-    <row r="73" ht="8" customHeight="1">
-      <c r="A73" s="28" t="inlineStr"/>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="12" t="n"/>
-    </row>
-    <row r="74" ht="10" customHeight="1"/>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="25" t="inlineStr">
-        <is>
-          <t>第4章　子の看護休暇・介護休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="26" t="inlineStr">
-        <is>
-          <t>（子の看護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="27" t="inlineStr">
-        <is>
-          <t>第12条　従業員は、小学校就学前の子が病気やけがをした場合、看護のため年5日（子が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
-        <is>
-          <t>2　子の看護休暇は、1日または半日単位で取得できる。</t>
-        </is>
-      </c>
-    </row>
     <row r="79" ht="8" customHeight="1"/>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>（介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="27" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、要介護状態にある家族の介護や通院付添のため、年5日（対象家族が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="27" t="inlineStr">
-        <is>
-          <t>2　介護休暇は、1日または半日単位で取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="8" customHeight="1">
-      <c r="A84" s="28" t="inlineStr"/>
-      <c r="B84" s="12" t="n"/>
-      <c r="C84" s="12" t="n"/>
-      <c r="D84" s="12" t="n"/>
-      <c r="E84" s="12" t="n"/>
-    </row>
-    <row r="85" ht="10" customHeight="1"/>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="25" t="inlineStr">
-        <is>
-          <t>第5章　復職・不利益取扱い禁止</t>
-        </is>
-      </c>
-    </row>
+    <row r="80" ht="8" customHeight="1">
+      <c r="A80" s="28" t="inlineStr"/>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+    </row>
+    <row r="81" ht="10" customHeight="1"/>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="25" t="inlineStr">
+        <is>
+          <t>第4章　子の看護等休暇・介護休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="26" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のため、年5日（子が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>2　子の看護等休暇は、1日または時間単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>（復職）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="48" customHeight="1">
+          <t>（介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>第14条　育児休業または介護休業を終了した従業員は、原則として休業前と同じ職務に復職させる。ただし、業務運営上やむを得ない場合は、同等の地位・待遇を有する職務に配置することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="8" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="26" t="inlineStr">
-        <is>
-          <t>（不利益取扱い禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="27" t="inlineStr">
-        <is>
-          <t>第15条　会社は、従業員が育児休業・介護休業・子の看護休暇・介護休暇を取得したことを理由として、解雇その他不利益な取扱いをしてはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="8" customHeight="1">
-      <c r="A93" s="28" t="inlineStr"/>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-      <c r="E93" s="12" t="n"/>
-    </row>
-    <row r="94" ht="10" customHeight="1"/>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="25" t="inlineStr">
-        <is>
-          <t>第6章　雑則</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="26" t="inlineStr">
-        <is>
-          <t>（制度の周知）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="27" t="inlineStr">
-        <is>
-          <t>第16条　会社は、本規程の内容を就業規則とともに従業員へ周知し、希望者が適切に制度を利用できるよう努めなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="8" customHeight="1"/>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="26" t="inlineStr">
-        <is>
-          <t>（個人情報保護）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="32" customHeight="1">
-      <c r="A100" s="27" t="inlineStr">
-        <is>
-          <t>第17条　会社は、休業申請や取得に関して知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="8" customHeight="1"/>
-    <row r="102" ht="8" customHeight="1">
-      <c r="A102" s="28" t="inlineStr"/>
-      <c r="B102" s="12" t="n"/>
-      <c r="C102" s="12" t="n"/>
-      <c r="D102" s="12" t="n"/>
-      <c r="E102" s="12" t="n"/>
-    </row>
-    <row r="103" ht="10" customHeight="1"/>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="25" t="inlineStr">
-        <is>
-          <t>附則</t>
+          <t>第13条　従業員は、要介護状態にある家族の介護や通院付添のため、年5日（対象家族が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>2　介護休暇は、1日または時間単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="8" customHeight="1"/>
+    <row r="91" ht="8" customHeight="1">
+      <c r="A91" s="28" t="inlineStr"/>
+      <c r="B91" s="12" t="n"/>
+      <c r="C91" s="12" t="n"/>
+      <c r="D91" s="12" t="n"/>
+      <c r="E91" s="12" t="n"/>
+    </row>
+    <row r="92" ht="10" customHeight="1"/>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="25" t="inlineStr">
+        <is>
+          <t>第4章の2　働き方の制限・措置</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="26" t="inlineStr">
+        <is>
+          <t>（所定外労働の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>第13条の2　小学校就学前の子を養育する従業員、または要介護状態にある家族を介護する従業員が請求した場合、事業の正常な運営を妨げる場合を除き、所定労働時間を超えて労働させない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>（時間外労働・深夜業の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>第13条の3　前条の従業員が請求した場合、時間外労働は1か月24時間、1年150時間を超えないものとし、深夜（午後10時から午前5時まで）に労働させない。ただし、法令に定める除外者はこの限りでない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>（短時間勤務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>第13条の4　3歳に満たない子を養育する従業員、または要介護状態にある家族を介護する従業員は、申し出により、所定労働時間を1日6時間とする短時間勤務を利用できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>（柔軟な働き方を実現するための措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>第13条の5　3歳から小学校就学前の子を養育する従業員に対し、会社は次の措置を講じ、従業員はいずれか1つを選択して利用できる。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="27" t="inlineStr">
         <is>
-          <t>1　本規程に定めのない事項は、育児・介護休業法、就業規則その他関係規程による。</t>
+          <t>1　始業・終業時刻の変更（時差出勤）</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="27" t="inlineStr">
         <is>
+          <t>2　養育両立支援休暇（年10日、時間単位で取得可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>（個別周知・意向確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>第13条の6　会社は、従業員から本人または配偶者の妊娠・出産の申出があったとき、及び子が3歳になる前の適切な時期に、育児休業等の制度を個別に周知し、取得や働き方の意向を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>2　会社は、従業員から家族の介護に直面した旨の申出があったとき、介護休業等の制度を個別に周知し、意向を確認する。また、40歳に達した従業員に対し、介護両立支援制度の情報を提供する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>（ハラスメントの防止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>第13条の7　会社は、妊娠・出産、育児休業・介護休業等の利用に関する言動により従業員の就業環境が害されることのないよう、相談体制の整備その他必要な措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="8" customHeight="1">
+      <c r="A115" s="28" t="inlineStr"/>
+      <c r="B115" s="12" t="n"/>
+      <c r="C115" s="12" t="n"/>
+      <c r="D115" s="12" t="n"/>
+      <c r="E115" s="12" t="n"/>
+    </row>
+    <row r="116" ht="10" customHeight="1"/>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="25" t="inlineStr">
+        <is>
+          <t>第5章　復職・不利益取扱い禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>（復職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="48" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>第14条　育児休業または介護休業を終了した従業員は、原則として休業前と同じ職務に復職させる。ただし、業務運営上やむを得ない場合は、同等の地位・待遇を有する職務に配置することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="26" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>第15条　会社は、従業員が育児休業・出生時育児休業・介護休業・子の看護等休暇・介護休暇その他本規程の制度を利用したことを理由として、解雇その他不利益な取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="8" customHeight="1">
+      <c r="A124" s="28" t="inlineStr"/>
+      <c r="B124" s="12" t="n"/>
+      <c r="C124" s="12" t="n"/>
+      <c r="D124" s="12" t="n"/>
+      <c r="E124" s="12" t="n"/>
+    </row>
+    <row r="125" ht="10" customHeight="1"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="25" t="inlineStr">
+        <is>
+          <t>第6章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="26" t="inlineStr">
+        <is>
+          <t>（制度の周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>第16条　会社は、本規程の内容を就業規則とともに従業員へ周知し、希望者が適切に制度を利用できるよう努めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="8" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="26" t="inlineStr">
+        <is>
+          <t>（個人情報保護）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="32" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、休業申請や取得に関して知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="28" t="inlineStr"/>
+      <c r="B133" s="12" t="n"/>
+      <c r="C133" s="12" t="n"/>
+      <c r="D133" s="12" t="n"/>
+      <c r="E133" s="12" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、育児・介護休業法、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
           <t>2　本規程は、令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="84">
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A77:E77"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
     <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A105:E105"/>
     <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A97:E97"/>
     <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A96:E96"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A117:E117"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5736,7 +5921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5909,59 +6094,65 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>（退職の申出）</t>
+          <t>（定年）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>第5条　従業員が自己都合により退職を希望する場合は、原則として退職希望日の30日前までに所定の退職届を提出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="8" customHeight="1"/>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="26" t="inlineStr">
-        <is>
-          <t>（引継ぎ義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>第6条　退職する従業員は、会社が指定する業務の引継ぎを誠実に行い、職務上の責任を果たさなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="8" customHeight="1"/>
+          <t>第4条の2　従業員の定年は満60歳とし、満60歳に達した日の属する月の末日をもって退職とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>2　定年に達した従業員が希望する場合は、高年齢者雇用安定法に基づき、満65歳まで継続雇用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>（退職の申出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>第5条　従業員が自己都合により退職を希望する場合は、円滑な引継ぎのため、原則として退職希望日の30日前までに所定の退職届を提出するよう努めなければならない。</t>
+        </is>
+      </c>
+    </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="26" t="inlineStr">
-        <is>
-          <t>（会社物品の返還）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="27" t="inlineStr">
-        <is>
-          <t>第7条　退職する従業員は、退職日までに会社から貸与された備品、制服、身分証、書類、電子機器その他の物品を返還しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="8" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="26" t="inlineStr">
-        <is>
-          <t>（退職証明書の交付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>2　前項にかかわらず、退職の効力は民法の定めによる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>（解雇予告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>第5条の2　会社が従業員を解雇する場合は、少なくとも30日前に予告するか、30日分以上の平均賃金（解雇予告手当）を支払う。ただし、労働基準監督署長の認定を受けた場合はこの限りでない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>第8条　従業員が退職した場合、本人の請求に基づき、労働基準法第22条に定める退職証明書を交付する。</t>
+          <t>2　予告の日数は、平均賃金を支払った日数分短縮することができる。</t>
         </is>
       </c>
     </row>
@@ -5969,14 +6160,14 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="26" t="inlineStr">
         <is>
-          <t>（賃金の精算）</t>
+          <t>（引継ぎ義務）</t>
         </is>
       </c>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>第9条　退職に際しては、労働基準法第23条に基づき、未払賃金その他の金銭を退職日から7日以内に支払う。</t>
+          <t>第6条　退職する従業員は、会社が指定する業務の引継ぎを誠実に行い、職務上の責任を果たさなければならない。</t>
         </is>
       </c>
     </row>
@@ -5984,44 +6175,44 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="26" t="inlineStr">
         <is>
-          <t>（秘密保持義務）</t>
+          <t>（会社物品の返還）</t>
         </is>
       </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="27" t="inlineStr">
         <is>
-          <t>第10条　退職した従業員は、在職中に知り得た会社の営業秘密、顧客情報、個人情報その他の秘密を退職後も漏洩してはならない。</t>
+          <t>第7条　退職する従業員は、退職日までに会社から貸与された備品、制服、身分証、書類、電子機器その他の物品を返還しなければならない。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="8" customHeight="1"/>
-    <row r="65" ht="8" customHeight="1">
-      <c r="A65" s="28" t="inlineStr"/>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12" t="n"/>
-    </row>
-    <row r="66" ht="10" customHeight="1"/>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="25" t="inlineStr">
-        <is>
-          <t>第3章　退職金</t>
-        </is>
-      </c>
-    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>（退職証明書の交付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>第8条　従業員が退職した場合、本人の請求に基づき、労働基準法第22条に定める退職証明書を交付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="26" t="inlineStr">
         <is>
-          <t>（支給対象者）</t>
+          <t>（賃金の精算）</t>
         </is>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="27" t="inlineStr">
         <is>
-          <t>第11条　勤続1年以上の従業員が退職した場合、会社は退職金を支給する。ただし、第15条に定める不支給事由に該当する場合は支給しない。</t>
+          <t>第9条　退職に際しては、労働基準法第23条に基づき、本人（死亡の場合は遺族）の請求があったときから7日以内に、未払賃金その他の金銭を支払う。</t>
         </is>
       </c>
     </row>
@@ -6029,341 +6220,393 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>（勤続年数の算定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
+          <t>（秘密保持義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="27" t="inlineStr">
         <is>
-          <t>第12条　勤続年数は、入社日から退職日までの期間により算定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
-        <is>
-          <t>2　1年未満の端数については次のとおりとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1　6か月未満の端数は切り捨てる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2　6か月以上の端数は1年に切り上げる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="8" customHeight="1"/>
+          <t>第10条　退職した従業員は、在職中に知り得た会社の営業秘密、顧客情報、個人情報その他の秘密を退職後も漏洩してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="8" customHeight="1">
+      <c r="A74" s="28" t="inlineStr"/>
+      <c r="B74" s="12" t="n"/>
+      <c r="C74" s="12" t="n"/>
+      <c r="D74" s="12" t="n"/>
+      <c r="E74" s="12" t="n"/>
+    </row>
+    <row r="75" ht="10" customHeight="1"/>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>第3章　退職金</t>
+        </is>
+      </c>
+    </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="26" t="inlineStr">
         <is>
-          <t>（退職金の算定方法）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
+          <t>（支給対象者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
       <c r="A78" s="27" t="inlineStr">
         <is>
-          <t>第13条　退職金の額は、次の算式により算定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>退職金 ＝ 退職時基本給 × 支給係数 × 勤続年数</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="8" customHeight="1"/>
+          <t>第11条　勤続1年以上の従業員が退職した場合、会社は退職金を支給する。ただし、第15条に定める不支給事由に該当する場合は支給しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>（勤続年数の算定）</t>
+        </is>
+      </c>
+    </row>
     <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="26" t="inlineStr">
-        <is>
-          <t>（支給係数）</t>
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>第12条　勤続年数は、入社日から退職日までの期間により算定する。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="27" t="inlineStr">
         <is>
+          <t>2　1年未満の端数については次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　6か月未満の端数は切り捨てる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　6か月以上の端数は1年に切り上げる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="8" customHeight="1"/>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
+          <t>（退職金の算定方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>第13条　退職金の額は、次の算式により算定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>退職金 ＝ 退職時基本給 × 支給係数 × 勤続年数</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>（支給係数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
           <t>第14条　支給係数は、勤続年数及び退職理由に応じて次のとおりとする。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="29" t="inlineStr">
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="29" t="inlineStr">
         <is>
           <t>勤続年数</t>
         </is>
       </c>
-      <c r="B83" s="33" t="inlineStr">
+      <c r="B92" s="33" t="inlineStr">
         <is>
           <t>自己都合</t>
         </is>
       </c>
-      <c r="C83" s="33" t="inlineStr">
+      <c r="C92" s="33" t="inlineStr">
         <is>
           <t>会社都合</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="31" t="inlineStr">
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="31" t="inlineStr">
         <is>
           <t>1年以上3年未満</t>
         </is>
       </c>
-      <c r="B84" s="34" t="inlineStr">
+      <c r="B93" s="34" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="C84" s="34" t="inlineStr">
+      <c r="C93" s="34" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="31" t="inlineStr">
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="31" t="inlineStr">
         <is>
           <t>3年以上6年未満</t>
         </is>
       </c>
-      <c r="B85" s="34" t="inlineStr">
+      <c r="B94" s="34" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="C85" s="34" t="inlineStr">
+      <c r="C94" s="34" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="31" t="inlineStr">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="31" t="inlineStr">
         <is>
           <t>6年以上9年未満</t>
         </is>
       </c>
-      <c r="B86" s="34" t="inlineStr">
+      <c r="B95" s="34" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="C86" s="34" t="inlineStr">
+      <c r="C95" s="34" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="31" t="inlineStr">
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="31" t="inlineStr">
         <is>
           <t>9年以上15年未満</t>
         </is>
       </c>
-      <c r="B87" s="34" t="inlineStr">
+      <c r="B96" s="34" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="C87" s="34" t="inlineStr">
+      <c r="C96" s="34" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="31" t="inlineStr">
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="31" t="inlineStr">
         <is>
           <t>15年以上25年未満</t>
         </is>
       </c>
-      <c r="B88" s="34" t="inlineStr">
+      <c r="B97" s="34" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="C88" s="34" t="inlineStr">
+      <c r="C97" s="34" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="31" t="inlineStr">
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="31" t="inlineStr">
         <is>
           <t>25年以上</t>
         </is>
       </c>
-      <c r="B89" s="34" t="inlineStr">
+      <c r="B98" s="34" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="C89" s="34" t="inlineStr">
+      <c r="C98" s="34" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="8" customHeight="1"/>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="26" t="inlineStr">
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="26" t="inlineStr">
         <is>
           <t>（不支給事由）</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="27" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
         <is>
           <t>第15条　従業員が次の各号のいずれかに該当する場合は、退職金を支給しない。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="27" t="inlineStr">
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="27" t="inlineStr">
         <is>
           <t>1　懲戒解雇された場合</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="27" t="inlineStr">
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="27" t="inlineStr">
         <is>
           <t>2　重大な背信行為により会社に著しい損害を与えた場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="27" t="inlineStr">
-        <is>
-          <t>3　虚偽の申告により雇用契約を締結したことが判明した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>（支給手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="27" t="inlineStr">
-        <is>
-          <t>第16条　退職金は、退職日から2か月以内に本人の指定口座に振り込む。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="27" t="inlineStr">
-        <is>
-          <t>2　会社は必要に応じて退職金の一部または全部を分割して支給することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="8" customHeight="1"/>
-    <row r="101" ht="8" customHeight="1">
-      <c r="A101" s="28" t="inlineStr"/>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
-      <c r="E101" s="12" t="n"/>
-    </row>
-    <row r="102" ht="10" customHeight="1"/>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="25" t="inlineStr">
-        <is>
-          <t>附則</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="27" t="inlineStr">
         <is>
+          <t>3　虚偽の申告により雇用契約を締結したことが判明した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="26" t="inlineStr">
+        <is>
+          <t>（支給手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>第16条　退職金は、退職日から2か月以内に本人の指定口座に振り込む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>2　会社は、本人の同意を得た場合に限り、退職金を分割して支給することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="8" customHeight="1">
+      <c r="A110" s="28" t="inlineStr"/>
+      <c r="B110" s="12" t="n"/>
+      <c r="C110" s="12" t="n"/>
+      <c r="D110" s="12" t="n"/>
+      <c r="E110" s="12" t="n"/>
+    </row>
+    <row r="111" ht="10" customHeight="1"/>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
           <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="27" t="inlineStr">
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
         <is>
           <t>2　本規程は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="64">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A82:E82"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A110:E110"/>
     <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
     <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A100:E100"/>
     <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A102:E102"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6683,7 +6926,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>4 サービス利用料金は１か月ごとに計算し、事業者が届ける請求書により、利用者は下記の方法により翌月26日までに支払うものとし、支払いを受けたときは領収証を発行します。</t>
+          <t>4 サービス利用料金は１か月ごとに計算し、事業者が届ける請求書により、利用者は下記の方法により重要事項説明書に定める期日までに支払うものとし、支払いを受けたときは領収証を発行します。</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7262,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>一 利用者がこの契約に定める利用料等の支払いを３か月以上遅延し、文書による支払い催告を行ったにもかかわらず、催告の日から７日以内にその支払いがなかった場合</t>
+          <t>一 利用者がこの契約に定める利用料等の支払いを３か月以上遅延し、文書による支払い催告を行ったにもかかわらず、催告の日から30日以内にその支払いがなかった場合</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7434,7 +7677,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>（1）障害福祉/高齢者介護サービスの提供のため</t>
+          <t>（1）介護サービスの提供のため</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7719,7 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>事業所は、障害福祉サービスを円滑に提供するため下記の事業者、機関等へ個人情報を提供することがあります。</t>
+          <t>事業所は、介護サービスを円滑に提供するため下記の事業者、機関等へ個人情報を提供することがあります。</t>
         </is>
       </c>
     </row>
@@ -7508,133 +7751,125 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>居宅介護・重度訪問介護契約書の第２条に定める契約期間及び法令の定めるところによる当該</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>契約の解約又は解除後の書類保存期間に相当する期間使用します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+          <t>指定訪問介護契約書の第２条に定める契約期間、及び法令の定めるところによる当該契約の解約又は解除後の書類保存期間に相当する期間使用します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　年　　月　　日</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>利用者</t>
         </is>
       </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>（住所）</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>（住所）</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr"/>
+          <t>（氏名）</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="12" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>（氏名）</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>（代理人または立会人等）</t>
         </is>
       </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>（住所）</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="20" t="inlineStr"/>
+      <c r="C33" s="21" t="inlineStr"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>（住所）</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr"/>
+          <t>（氏名）</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
+        </is>
+      </c>
       <c r="D34" s="12" t="n"/>
       <c r="E34" s="12" t="n"/>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="21" t="inlineStr"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>（氏名）</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="C29:E29"/>
+  <mergeCells count="25">
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="C31:E31"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A8:E8"/>
-    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -8937,7 +9172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9074,456 +9309,464 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="27" t="inlineStr">
         <is>
-          <t>第4条　会社は、常時50人未満の事業場であるため法令上の衛生管理者選任義務はないが、必要に応じて衛生推進者を指名し、従業員の健康保持増進活動を推進することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="8" customHeight="1"/>
-    <row r="43" ht="8" customHeight="1">
-      <c r="A43" s="28" t="inlineStr"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-    </row>
-    <row r="44" ht="10" customHeight="1"/>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
+          <t>第4条　会社は、常時10人以上50人未満の労働者を使用する事業場として、労働安全衛生法に基づき衛生推進者を選任し、その氏名を事業場に掲示して従業員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>2　衛生推進者は、健康診断、職場環境の点検、安全衛生教育その他衛生に関する業務を担当する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="8" customHeight="1">
+      <c r="A44" s="28" t="inlineStr"/>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+    </row>
+    <row r="45" ht="10" customHeight="1"/>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>第3章　健康管理</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="26" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>（健康診断）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>第5条　会社は、労働安全衛生法に基づき、従業員に次の健康診断を実施する。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>1　雇入時健康診断（入社時）</t>
+          <t>第5条　会社は、労働安全衛生法に基づき、従業員に次の健康診断を実施する。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>2　定期健康診断（年1回。ただし夜勤業務に従事する者については年2回）</t>
+          <t>1　雇入時健康診断（入社時）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>3　特定業務従事者健康診断（必要に応じて）</t>
+          <t>2　定期健康診断（年1回。ただし夜勤業務に従事する者については年2回）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="27" t="inlineStr">
         <is>
+          <t>3　特定業務従事者健康診断（必要に応じて）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
           <t>2　健康診断の費用は会社が負担する。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="8" customHeight="1"/>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="26" t="inlineStr">
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>（診断結果への対応）</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="27" t="inlineStr">
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>第6条　会社は、健康診断の結果に基づき、必要に応じて就業上の措置を講じる。従業員は医師の意見に従い、就業制限や治療を受けなければならない。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="8" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="26" t="inlineStr">
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="26" t="inlineStr">
         <is>
           <t>（ストレスチェック）</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>第7条　会社は、従業員数50人未満のため法定義務はないが、必要に応じてストレスチェックを実施し、結果に基づき職場環境改善や個別対応を行うことができる。</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="8" customHeight="1"/>
-    <row r="59" ht="8" customHeight="1">
-      <c r="A59" s="28" t="inlineStr"/>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-    </row>
-    <row r="60" ht="10" customHeight="1"/>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="25" t="inlineStr">
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="8" customHeight="1">
+      <c r="A60" s="28" t="inlineStr"/>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+    </row>
+    <row r="61" ht="10" customHeight="1"/>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>第4章　職場環境の整備</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="26" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>（作業環境管理）</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="27" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>第8条　会社は、職場の換気、採光、照明、温度、騒音等の環境を適正に維持する。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="8" customHeight="1"/>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="26" t="inlineStr">
+    <row r="65" ht="8" customHeight="1"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="26" t="inlineStr">
         <is>
           <t>（作業方法の改善）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="27" t="inlineStr">
-        <is>
-          <t>第9条　会社は、業務に伴う危険や健康障害を防止するため、作業方法を改善し、安全衛生教育を実施する。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="27" t="inlineStr">
         <is>
+          <t>第9条　会社は、業務に伴う危険や健康障害を防止するため、作業方法を改善し、安全衛生教育を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
           <t>2　特に介護業務においては、腰痛予防、福祉用具の適切な使用、送迎業務における車両運転の安全確保に努める。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="8" customHeight="1"/>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="26" t="inlineStr">
+    <row r="69" ht="8" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="26" t="inlineStr">
         <is>
           <t>（感染症予防）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="27" t="inlineStr">
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
         <is>
           <t>第10条　会社は、インフルエンザ、新型コロナウイルスその他感染症の予防に努め、必要に応じてマスク着用、手指消毒、在宅勤務、出勤停止等の措置を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="8" customHeight="1"/>
-    <row r="72" ht="8" customHeight="1">
-      <c r="A72" s="28" t="inlineStr"/>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="12" t="n"/>
-      <c r="D72" s="12" t="n"/>
-      <c r="E72" s="12" t="n"/>
-    </row>
-    <row r="73" ht="10" customHeight="1"/>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="25" t="inlineStr">
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="8" customHeight="1">
+      <c r="A73" s="28" t="inlineStr"/>
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="12" t="n"/>
+      <c r="D73" s="12" t="n"/>
+      <c r="E73" s="12" t="n"/>
+    </row>
+    <row r="74" ht="10" customHeight="1"/>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
         <is>
           <t>第5章　安全衛生教育</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="26" t="inlineStr">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="26" t="inlineStr">
         <is>
           <t>（教育の実施）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
-        <is>
-          <t>第11条　会社は、従業員に対して次の安全衛生教育を実施する。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="27" t="inlineStr">
         <is>
-          <t>1　雇入時教育（安全衛生に関する基本事項）</t>
+          <t>第11条　会社は、従業員に対して次の安全衛生教育を実施する。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="27" t="inlineStr">
         <is>
-          <t>2　配置転換時教育（新しい業務に伴う危険防止）</t>
+          <t>1　雇入時教育（安全衛生に関する基本事項）</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="27" t="inlineStr">
         <is>
-          <t>3　作業内容変更時教育（介護・送迎業務における腰痛防止、交通安全等）</t>
+          <t>2　配置転換時教育（新しい業務に伴う危険防止）</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="27" t="inlineStr">
         <is>
+          <t>3　作業内容変更時教育（介護・送迎業務における腰痛防止、交通安全等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
           <t>4　定期教育（年1回以上、安全衛生全般に関する教育）</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="8" customHeight="1"/>
-    <row r="82" ht="8" customHeight="1">
-      <c r="A82" s="28" t="inlineStr"/>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="12" t="n"/>
-      <c r="E82" s="12" t="n"/>
-    </row>
-    <row r="83" ht="10" customHeight="1"/>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="25" t="inlineStr">
+    <row r="82" ht="8" customHeight="1"/>
+    <row r="83" ht="8" customHeight="1">
+      <c r="A83" s="28" t="inlineStr"/>
+      <c r="B83" s="12" t="n"/>
+      <c r="C83" s="12" t="n"/>
+      <c r="D83" s="12" t="n"/>
+      <c r="E83" s="12" t="n"/>
+    </row>
+    <row r="84" ht="10" customHeight="1"/>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="25" t="inlineStr">
         <is>
           <t>第6章　労働災害への対応</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="26" t="inlineStr">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="26" t="inlineStr">
         <is>
           <t>（災害発生時の措置）</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="27" t="inlineStr">
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
         <is>
           <t>第12条　労働災害が発生した場合、従業員は直ちに上長に報告し、会社は応急措置を講じ、必要に応じて関係行政官庁へ報告する。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="8" customHeight="1"/>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="26" t="inlineStr">
+    <row r="88" ht="8" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="26" t="inlineStr">
         <is>
           <t>（再発防止）</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="27" t="inlineStr">
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
         <is>
           <t>第13条　会社は、労働災害が発生した場合、その原因を調査し、再発防止策を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="8" customHeight="1"/>
-    <row r="91" ht="8" customHeight="1">
-      <c r="A91" s="28" t="inlineStr"/>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="12" t="n"/>
-      <c r="D91" s="12" t="n"/>
-      <c r="E91" s="12" t="n"/>
-    </row>
-    <row r="92" ht="10" customHeight="1"/>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="25" t="inlineStr">
+    <row r="91" ht="8" customHeight="1"/>
+    <row r="92" ht="8" customHeight="1">
+      <c r="A92" s="28" t="inlineStr"/>
+      <c r="B92" s="12" t="n"/>
+      <c r="C92" s="12" t="n"/>
+      <c r="D92" s="12" t="n"/>
+      <c r="E92" s="12" t="n"/>
+    </row>
+    <row r="93" ht="10" customHeight="1"/>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="25" t="inlineStr">
         <is>
           <t>第7章　健康保持・メンタルヘルス</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="26" t="inlineStr">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="26" t="inlineStr">
         <is>
           <t>（過重労働対策）</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="27" t="inlineStr">
+    <row r="96" ht="32" customHeight="1">
+      <c r="A96" s="27" t="inlineStr">
         <is>
           <t>第14条　会社は、時間外労働や深夜労働が従業員の心身に過度の負担を与えないように管理し、長時間労働が認められる場合は速やかに対応する。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="26" t="inlineStr">
         <is>
           <t>（メンタルヘルス対応）</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="27" t="inlineStr">
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
         <is>
           <t>第15条　会社は、従業員がうつ病、適応障害その他のメンタル不調を抱えた場合、医師の診断や専門家の意見を踏まえ、必要な就業上の措置（休職・勤務軽減・復職支援等）を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="8" customHeight="1"/>
-    <row r="100" ht="8" customHeight="1">
-      <c r="A100" s="28" t="inlineStr"/>
-      <c r="B100" s="12" t="n"/>
-      <c r="C100" s="12" t="n"/>
-      <c r="D100" s="12" t="n"/>
-      <c r="E100" s="12" t="n"/>
-    </row>
-    <row r="101" ht="10" customHeight="1"/>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="25" t="inlineStr">
+    <row r="100" ht="8" customHeight="1"/>
+    <row r="101" ht="8" customHeight="1">
+      <c r="A101" s="28" t="inlineStr"/>
+      <c r="B101" s="12" t="n"/>
+      <c r="C101" s="12" t="n"/>
+      <c r="D101" s="12" t="n"/>
+      <c r="E101" s="12" t="n"/>
+    </row>
+    <row r="102" ht="10" customHeight="1"/>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="25" t="inlineStr">
         <is>
           <t>第8章　その他</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="26" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="26" t="inlineStr">
         <is>
           <t>（健康情報の管理）</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="27" t="inlineStr">
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
         <is>
           <t>第16条　健康診断やストレスチェックの結果、相談等により得た従業員の個人情報は厳格に管理し、本人の同意なく第三者に開示してはならない。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="8" customHeight="1"/>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="26" t="inlineStr">
+    <row r="106" ht="8" customHeight="1"/>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="26" t="inlineStr">
         <is>
           <t>（不利益取扱いの禁止）</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="27" t="inlineStr">
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="27" t="inlineStr">
         <is>
           <t>第17条　会社は、従業員が健康診断、感染症予防措置、安全衛生教育等を受けたことを理由に、不利益取扱いをしてはならない。</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="8" customHeight="1"/>
-    <row r="109" ht="8" customHeight="1">
-      <c r="A109" s="28" t="inlineStr"/>
-      <c r="B109" s="12" t="n"/>
-      <c r="C109" s="12" t="n"/>
-      <c r="D109" s="12" t="n"/>
-      <c r="E109" s="12" t="n"/>
-    </row>
-    <row r="110" ht="10" customHeight="1"/>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="25" t="inlineStr">
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="8" customHeight="1">
+      <c r="A110" s="28" t="inlineStr"/>
+      <c r="B110" s="12" t="n"/>
+      <c r="C110" s="12" t="n"/>
+      <c r="D110" s="12" t="n"/>
+      <c r="E110" s="12" t="n"/>
+    </row>
+    <row r="111" ht="10" customHeight="1"/>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="25" t="inlineStr">
         <is>
           <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="27" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、労働基準法、労働安全衛生法その他関係法令による。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="27" t="inlineStr">
         <is>
+          <t>1　本規程に定めのない事項は、労働基準法、労働安全衛生法その他関係法令による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
           <t>2　本規程は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A98:E98"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A84:E84"/>
     <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A74:E74"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A101:E101"/>
     <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A42:E42"/>
     <mergeCell ref="A113:E113"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A91:E91"/>
     <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9907,7 +10150,7 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="27" t="inlineStr">
         <is>
-          <t>3　禁錮以上の刑に処せられ、その判決が確定した場合。</t>
+          <t>3　拘禁刑以上の刑に処せられ、その判決が確定した場合。</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10794,267 +11037,273 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>2　その後も、継続勤務ごとに6か月経過するごとに10日の年次有給休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
+          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>（取得方法）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="27" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="8" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="26" t="inlineStr">
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>（時季変更権）</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="27" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="8" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="26" t="inlineStr">
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>（時間単位年休）</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇の一部を時間単位で取得させることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="8" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="26" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>（計画的付与）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="27" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="8" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="26" t="inlineStr">
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>（年5日の取得義務）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="27" t="inlineStr">
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="27" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="8" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="26" t="inlineStr">
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="26" t="inlineStr">
         <is>
           <t>（有効期限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="27" t="inlineStr">
         <is>
+          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
           <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="8" customHeight="1"/>
-    <row r="61" ht="8" customHeight="1">
-      <c r="A61" s="28" t="inlineStr"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="12" t="n"/>
-    </row>
-    <row r="62" ht="10" customHeight="1"/>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="25" t="inlineStr">
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="28" t="inlineStr"/>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="12" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="12" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>第3章　特別休暇</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="26" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="26" t="inlineStr">
         <is>
           <t>（慶弔休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="27" t="inlineStr">
-        <is>
-          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="27" t="inlineStr">
-        <is>
-          <t>1　本人の結婚：5日</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="27" t="inlineStr">
         <is>
-          <t>2　子女の結婚：2日</t>
+          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>3　配偶者の死亡：5日</t>
+          <t>1　本人の結婚：5日</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="27" t="inlineStr">
         <is>
-          <t>4　父母・子の死亡：5日</t>
+          <t>2　子女の結婚：2日</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="27" t="inlineStr">
         <is>
-          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+          <t>3　配偶者の死亡：5日</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="27" t="inlineStr">
         <is>
-          <t>6　その他会社が必要と認めた場合：別途定める</t>
+          <t>4　父母・子の死亡：5日</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="27" t="inlineStr">
         <is>
+          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>6　その他会社が必要と認めた場合：別途定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
           <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="8" customHeight="1"/>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="26" t="inlineStr">
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="26" t="inlineStr">
         <is>
           <t>（産前産後休業）</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="27" t="inlineStr">
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
         <is>
           <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="8" customHeight="1"/>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="26" t="inlineStr">
+    <row r="78" ht="8" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t>（育児休業・介護休業）</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
         <is>
           <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="8" customHeight="1"/>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>（子の看護休暇・介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="27" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、小学校就学前の子1人につき年間5日（2人以上は10日）の子の看護休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
+    <row r="81" ht="8" customHeight="1"/>
     <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="27" t="inlineStr">
-        <is>
-          <t>2　要介護家族については、年間5日の介護休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="26" t="inlineStr">
-        <is>
-          <t>（病気休暇）</t>
+      <c r="A82" s="26" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇・介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="27" t="inlineStr">
         <is>
-          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
+          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
         </is>
       </c>
     </row>
@@ -11062,14 +11311,14 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>（公務・公用休暇）</t>
+          <t>（病気休暇）</t>
         </is>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
+          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
         </is>
       </c>
     </row>
@@ -11077,14 +11326,14 @@
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>（感染症予防に伴う休暇）</t>
+          <t>（公務・公用休暇）</t>
         </is>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
+          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
         </is>
       </c>
     </row>
@@ -11092,317 +11341,394 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>（誕生日休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
+          <t>（感染症予防に伴う休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
       <c r="A94" s="27" t="inlineStr">
         <is>
-          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
+          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
         </is>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="27" t="inlineStr">
-        <is>
-          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="8" customHeight="1"/>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="26" t="inlineStr">
-        <is>
-          <t>（その他の特別休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="32" customHeight="1">
-      <c r="A99" s="27" t="inlineStr">
-        <is>
-          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="8" customHeight="1"/>
-    <row r="101" ht="8" customHeight="1">
-      <c r="A101" s="28" t="inlineStr"/>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
-      <c r="E101" s="12" t="n"/>
-    </row>
-    <row r="102" ht="10" customHeight="1"/>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="25" t="inlineStr">
-        <is>
-          <t>第4章　手続</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="26" t="inlineStr">
-        <is>
-          <t>（申請手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="27" t="inlineStr">
-        <is>
-          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="8" customHeight="1"/>
+          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>（生理休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>（育児時間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>（母性健康管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="26" t="inlineStr">
+        <is>
+          <t>（誕生日休暇）</t>
+        </is>
+      </c>
+    </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="26" t="inlineStr">
-        <is>
-          <t>（診断書等の提出）</t>
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="32" customHeight="1">
       <c r="A108" s="27" t="inlineStr">
         <is>
-          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="27" t="inlineStr">
         <is>
+          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="8" customHeight="1"/>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>（その他の特別休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="8" customHeight="1"/>
+    <row r="114" ht="8" customHeight="1">
+      <c r="A114" s="28" t="inlineStr"/>
+      <c r="B114" s="12" t="n"/>
+      <c r="C114" s="12" t="n"/>
+      <c r="D114" s="12" t="n"/>
+      <c r="E114" s="12" t="n"/>
+    </row>
+    <row r="115" ht="10" customHeight="1"/>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="25" t="inlineStr">
+        <is>
+          <t>第4章　手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>（申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="26" t="inlineStr">
+        <is>
+          <t>（診断書等の提出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
           <t>1　私傷病により連続して3日以上欠勤するとき</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="27" t="inlineStr">
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
         <is>
           <t>2　休職を申請するとき</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="27" t="inlineStr">
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
         <is>
           <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="27" t="inlineStr">
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="27" t="inlineStr">
         <is>
           <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="27" t="inlineStr">
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="27" t="inlineStr">
         <is>
           <t>5　会社が安全衛生管理上必要と認めたとき</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="27" t="inlineStr">
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
         <is>
           <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="27" t="inlineStr">
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
         <is>
           <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="27" t="inlineStr">
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="27" t="inlineStr">
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="27" t="inlineStr">
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="8" customHeight="1">
-      <c r="A120" s="28" t="inlineStr"/>
-      <c r="B120" s="12" t="n"/>
-      <c r="C120" s="12" t="n"/>
-      <c r="D120" s="12" t="n"/>
-      <c r="E120" s="12" t="n"/>
-    </row>
-    <row r="121" ht="10" customHeight="1"/>
-    <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="25" t="inlineStr">
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="28" t="inlineStr"/>
+      <c r="B133" s="12" t="n"/>
+      <c r="C133" s="12" t="n"/>
+      <c r="D133" s="12" t="n"/>
+      <c r="E133" s="12" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="25" t="inlineStr">
         <is>
           <t>第5章　その他</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="26" t="inlineStr">
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="26" t="inlineStr">
         <is>
           <t>（不利益取扱い禁止）</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="27" t="inlineStr">
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
         <is>
           <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="8" customHeight="1"/>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="26" t="inlineStr">
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="26" t="inlineStr">
         <is>
           <t>（休暇中の待遇）</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="27" t="inlineStr">
+    <row r="140" ht="32" customHeight="1">
+      <c r="A140" s="27" t="inlineStr">
         <is>
           <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="8" customHeight="1"/>
-    <row r="129" ht="8" customHeight="1">
-      <c r="A129" s="28" t="inlineStr"/>
-      <c r="B129" s="12" t="n"/>
-      <c r="C129" s="12" t="n"/>
-      <c r="D129" s="12" t="n"/>
-      <c r="E129" s="12" t="n"/>
-    </row>
-    <row r="130" ht="10" customHeight="1"/>
-    <row r="131" ht="30" customHeight="1">
-      <c r="A131" s="25" t="inlineStr">
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="8" customHeight="1">
+      <c r="A142" s="28" t="inlineStr"/>
+      <c r="B142" s="12" t="n"/>
+      <c r="C142" s="12" t="n"/>
+      <c r="D142" s="12" t="n"/>
+      <c r="E142" s="12" t="n"/>
+    </row>
+    <row r="143" ht="10" customHeight="1"/>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="25" t="inlineStr">
         <is>
           <t>附則</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="27" t="inlineStr">
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="27" t="inlineStr">
         <is>
           <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="27" t="inlineStr">
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="27" t="inlineStr">
         <is>
           <t>2　本規程は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="94">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A136:E136"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A115:E115"/>
     <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
     <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
     <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A127:E127"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
     <mergeCell ref="A116:E116"/>
     <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A140:E140"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A68:E68"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -20,7 +20,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6629,6 +6631,1375 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E128"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>就業規則</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規則は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）に勤務する従業員の就業に関する基本事項を定め、労務管理の適正化、従業員の生活の安定および業務の円滑な運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規則における用語の定義は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>1　「従業員」とは、会社に雇用される者をいう（有期・無期、所定労働時間の長短を問わない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>2　「管理監督者」とは、労働基準法第41条に定める者をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>3　その他の用語の詳細は「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>第3条　本規則は、会社に雇用されるすべての従業員に適用する。管理監督者等の一部については法令に従い適用除外とし、詳細は「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>（周知・改廃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>第4条　本規則および各規程は、社内掲示・イントラネット等により周知する。改廃は労働基準法に基づく手続（意見聴取・届出等）を経て行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="28" t="inlineStr"/>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="10" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>第2章　勤務</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>（勤務体制：1か月単位の変形労働時間制）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>第5条　会社は一か月単位の変形労働時間制を採用する。対象者、計算期間、各日・各週の所定労働時間の決定方法、勤務割表の作成・通知方法その他の詳細は「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>（所定労働時間・休憩）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>第6条　所定労働時間は1日8時間とする。休憩は原則として6時間を超える勤務の場合1時間、夜勤勤務の場合2時間とし、取得方法は「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>（休日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>第7条　休日は月10日を原則とし、このうち法定休日は会社の定める日とする（4週間を通じ少なくとも4日）。振替休日・代休の取扱いは「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>（時間外・休日・深夜労働）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>第8条　業務上必要がある場合、会社は36協定に基づき時間外労働および休日労働を命じることがある。22時から翌5時までの労働については法定割増賃金を支給する。手当の区分・額等は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>（出退勤記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>第9条　従業員は会社の指定する方法により出退勤を記録しなければならない。記録方法、訂正手続等は「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>（配置転換・出向・転勤）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>第10条　会社は業務上の必要により配置転換、出向、転勤等を命ずることがある。手続・配慮事項は「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="28" t="inlineStr"/>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="12" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="12" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>第3章　服務</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="26" t="inlineStr">
+        <is>
+          <t>（服務規律）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>第11条　従業員は、法令、本規則および各種規程並びに会社の指示に従い、誠実かつ公正に職務を遂行し、職場秩序を維持しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>（ハラスメントの禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、セクシュアルハラスメント、パワーハラスメントその他一切のハラスメント行為を行ってはならない。防止体制、相談・調査・再発防止等は「ハラスメント防止規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="26" t="inlineStr">
+        <is>
+          <t>（秘密情報・個人情報の保護）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、在職中および退職後において、業務上知り得た秘密情報・個人情報を漏えいしてはならない。範囲、管理措置、違反時の取扱いは「情報管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>（競業避止・利益相反）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="48" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>第14条　会社が指定する者は、在職中および退職後一定期間、会社の指定する地域において競業行為を行ってはならない。兼業・副業、利益相反の管理は「競業避止規程」および「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="8" customHeight="1">
+      <c r="A78" s="28" t="inlineStr"/>
+      <c r="B78" s="12" t="n"/>
+      <c r="C78" s="12" t="n"/>
+      <c r="D78" s="12" t="n"/>
+      <c r="E78" s="12" t="n"/>
+    </row>
+    <row r="79" ht="10" customHeight="1"/>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>第4章　休暇・休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>（年次有給休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>第15条　従業員には労働基準法に基づく年次有給休暇を付与する。付与日、計画的付与、時季変更、半日・時間単位付与等は「休暇規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
+          <t>（特別休暇・法定休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>第16条　慶弔休暇、病気休暇、産前産後休暇、育児休業、介護休業、子の看護等休暇等の付与・手続は「休暇規程」および「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="8" customHeight="1">
+      <c r="A87" s="28" t="inlineStr"/>
+      <c r="B87" s="12" t="n"/>
+      <c r="C87" s="12" t="n"/>
+      <c r="D87" s="12" t="n"/>
+      <c r="E87" s="12" t="n"/>
+    </row>
+    <row r="88" ht="10" customHeight="1"/>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="25" t="inlineStr">
+        <is>
+          <t>第5章　賃金</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>（賃金の構成・決定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>第17条　賃金は、基本給、諸手当、賞与その他会社の定めるものから構成する。種類、額、計算・支給方法、欠勤・遅刻等の控除、割増賃金の算定は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>（締切日・支払日・支払方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>第18条　賃金の締切日は毎月末日とし、翌月27日に支払う。支払日が土曜日、日曜日または祝日に当たるときは、直前の平日に繰り上げて支払う。支払方法は、従業員の同意を得て、従業員が指定する銀行口座への振込による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="26" t="inlineStr">
+        <is>
+          <t>（賃金控除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>第19条　法令に基づく控除のほか、会社と労使協定を締結した場合に限り賃金控除を行う。控除項目等は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="8" customHeight="1">
+      <c r="A99" s="28" t="inlineStr"/>
+      <c r="B99" s="12" t="n"/>
+      <c r="C99" s="12" t="n"/>
+      <c r="D99" s="12" t="n"/>
+      <c r="E99" s="12" t="n"/>
+    </row>
+    <row r="100" ht="10" customHeight="1"/>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="25" t="inlineStr">
+        <is>
+          <t>第6章　安全衛生</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="26" t="inlineStr">
+        <is>
+          <t>（安全衛生管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="48" customHeight="1">
+      <c r="A103" s="27" t="inlineStr">
+        <is>
+          <t>第20条　会社は労働安全衛生法その他関係法令に基づき、従業員の安全と健康の確保に努める。従業員は会社の措置に協力しなければならない。体制、健康診断、就業上の措置等は「安全衛生規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="8" customHeight="1"/>
+    <row r="105" ht="8" customHeight="1">
+      <c r="A105" s="28" t="inlineStr"/>
+      <c r="B105" s="12" t="n"/>
+      <c r="C105" s="12" t="n"/>
+      <c r="D105" s="12" t="n"/>
+      <c r="E105" s="12" t="n"/>
+    </row>
+    <row r="106" ht="10" customHeight="1"/>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="25" t="inlineStr">
+        <is>
+          <t>第7章　懲戒</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>（懲戒の基本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>第21条　従業員が服務規律に違反した場合、情状に応じて懲戒処分を行うことがある。懲戒の種類、事由、手続、弁明の機会付与等は「懲戒規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>2　懲戒により減給を命ずる場合、1回の額は平均賃金の1日分の半額を超えず、総額は1賃金支払期における賃金総額の1/10を超えない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="8" customHeight="1">
+      <c r="A112" s="28" t="inlineStr"/>
+      <c r="B112" s="12" t="n"/>
+      <c r="C112" s="12" t="n"/>
+      <c r="D112" s="12" t="n"/>
+      <c r="E112" s="12" t="n"/>
+    </row>
+    <row r="113" ht="10" customHeight="1"/>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="25" t="inlineStr">
+        <is>
+          <t>第8章　退職・解雇</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
+        <is>
+          <t>（退職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="48" customHeight="1">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>第22条　従業員が自己都合により退職する場合は、円滑な引継ぎのため、原則として30日前までに、書面（電磁的方法を含む）にて会社に届け出るよう努めなければならない。定年、退職時の有給休暇の取扱い、業務引継、貸与物の返還等は「退職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="8" customHeight="1"/>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>（解雇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>第23条　会社は、業務遂行困難、職務不良、服務規律違反その他やむを得ない事由がある場合に解雇を行うことがある。解雇事由、手続、予告・予告手当、整理解雇の要件等は「退職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="26" t="inlineStr">
+        <is>
+          <t>（退職時証明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>第24条　従業員が退職に際し、在職期間・業務の種類・地位・賃金・事由等の退職証明書の交付を請求したときは、法令に従い遅滞なく交付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="8" customHeight="1">
+      <c r="A124" s="28" t="inlineStr"/>
+      <c r="B124" s="12" t="n"/>
+      <c r="C124" s="12" t="n"/>
+      <c r="D124" s="12" t="n"/>
+      <c r="E124" s="12" t="n"/>
+    </row>
+    <row r="125" ht="10" customHeight="1"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t>第25条　本規則に定めのない事項は、労働基準法その他関係法令および会社の各規程による。制定・改廃の履歴は「規程管理台帳」に記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>第26条　本規則は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　就業規則</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>安全衛生規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>【第1条（目的）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>本規程は、株式会社dhpケアマネジメント　いいかいごにおける訪問介護・居宅サービス・サポート付き住宅運営において、従業者および利用者の安全と健康を確保し、事故防止、感染症対策、労働災害防止を推進することを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>【第2条（適用範囲）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>本規程は、当法人に所属する全従業者（常勤・非常勤・登録ヘルパー・夜勤スタッフ・看護職・事務職）および協力事業者に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>【第3条（安全衛生管理体制）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>1. 法人代表者は安全衛生管理の最高責任者である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>2. 事業所管理者を安全衛生責任者とし、日常運営における安全衛生管理を統括する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>3. 必要に応じて安全衛生委員会を設置し、月1回協議を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>4. 委員会構成：管理者（委員長）、サービス提供責任者、看護職代表、介護職代表、夜勤代表、事務代表、管理部（事務局）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="8" customHeight="1">
+      <c r="A39" s="28" t="inlineStr"/>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="10" customHeight="1"/>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>第2章　安全管理に関する基本方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>【第4条（安全確保）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>1. 利用者の転倒・転落・誤嚥等の事故防止のため、環境整備と見守り体制を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>2. 事故予兆の早期発見のため、報告体制を整備する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>3. 職員の安全確保のため、以下を徹底する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・腰痛予防（ノーリフティング・補助具使用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・夜勤単独リスク対策</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・暴力・ハラスメント防止対策</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・移動時の交通安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>【第5条（リスクアセスメント）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>以下を月1回以上評価する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>1. 転倒・転落リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>2. 徘徊・不穏リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>3. 火災・災害時の避難リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>4. 福祉用具・医療機器リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>5. 夜間緊急リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="8" customHeight="1"/>
+    <row r="59" ht="8" customHeight="1">
+      <c r="A59" s="28" t="inlineStr"/>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12" t="n"/>
+    </row>
+    <row r="60" ht="10" customHeight="1"/>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>第3章　衛生管理に関する基本事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t>【第6条（職員の健康管理）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>1. 年1回以上の健康診断を受診する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>2. 発熱・嘔吐・感染症疑いがある場合は出勤を禁止する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>3. 夜勤者の連続勤務禁止、長時間労働防止を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>【第7条（感染症予防）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>1. 手洗い・手指消毒・PPEなど標準予防策を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>2. 感染発生時は隔離・動線確保・消毒を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>3. 新型コロナ・インフル・ノロ等は感染症マニュアルに従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="8" customHeight="1">
+      <c r="A72" s="28" t="inlineStr"/>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="12" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+    </row>
+    <row r="73" ht="10" customHeight="1"/>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>第4章　設備・環境衛生の管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>【第8条（環境整備）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>1. 廊下・階段・共有部の整理整頓を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>2. 福祉用具は定期点検を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>3. 温度・湿度・換気を適切に管理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>4. 消防設備は年1回以上点検する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>【第9条（清掃・衛生管理）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>1. 共有部・トイレ・浴室の清掃を毎日行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>2. 嘔吐物・感染性廃棄物はマニュアルに従い処理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="8" customHeight="1">
+      <c r="A85" s="28" t="inlineStr"/>
+      <c r="B85" s="12" t="n"/>
+      <c r="C85" s="12" t="n"/>
+      <c r="D85" s="12" t="n"/>
+      <c r="E85" s="12" t="n"/>
+    </row>
+    <row r="86" ht="10" customHeight="1"/>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="25" t="inlineStr">
+        <is>
+          <t>第5章　職員教育・研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="26" t="inlineStr">
+        <is>
+          <t>【第10条（教育研修）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>1. 安全衛生・緊急対応・感染症・腰痛予防の研修を年2回以上行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>2. 新入職員は初期研修で安全衛生教育を必須とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>3. 研修記録は5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>【第11条（情報共有）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>・事故・ヒヤリハットは速やかに共有し、再発防止策を検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>・委員会の審議内容は全従業者に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="8" customHeight="1">
+      <c r="A97" s="28" t="inlineStr"/>
+      <c r="B97" s="12" t="n"/>
+      <c r="C97" s="12" t="n"/>
+      <c r="D97" s="12" t="n"/>
+      <c r="E97" s="12" t="n"/>
+    </row>
+    <row r="98" ht="10" customHeight="1"/>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="25" t="inlineStr">
+        <is>
+          <t>第6章　事故・災害・緊急時対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>【第12条（事故対応）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>1. 事故発生時は応急処置、管理者報告、家族連絡、記録を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="27" t="inlineStr">
+        <is>
+          <t>2. 必要に応じ医療機関へ搬送する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="26" t="inlineStr">
+        <is>
+          <t>【第13条（災害対応）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>1. 火災・地震・風水害等の発生時は避難計画に従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
+          <t>2. 夜勤帯は緊急連絡体制を強化する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>【第14条（緊急時マニュアル）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>全従業者は緊急時対応マニュアルを理解し、定期的に訓練を受ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="8" customHeight="1"/>
+    <row r="111" ht="8" customHeight="1">
+      <c r="A111" s="28" t="inlineStr"/>
+      <c r="B111" s="12" t="n"/>
+      <c r="C111" s="12" t="n"/>
+      <c r="D111" s="12" t="n"/>
+      <c r="E111" s="12" t="n"/>
+    </row>
+    <row r="112" ht="10" customHeight="1"/>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="25" t="inlineStr">
+        <is>
+          <t>第7章　附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="26" t="inlineStr">
+        <is>
+          <t>【第15条（規程の見直し）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>本規程は年1回、または必要時に見直しを行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="8" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>【施行日】</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="76">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　安全衛生規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -22,7 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +93,15 @@
       <name val="Arial"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -127,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -222,6 +232,27 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -8000,6 +8031,1494 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E207"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>感染症対策指針</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ．平常時の対策</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>1．総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>（1）目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>訪問介護事業者には、利用者の居宅において、利用者の健康と安全を守るための支援が求められている。訪問介護員は複数の利用者宅を訪問するため、職員が感染を媒介するおそれがあり、利用者の安全確保の観点から感染対策はきわめて重要である。感染を未然に防止し、発生した場合には感染症が拡大しないよう可及的速やかに対応する体制を構築することが必要である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>この指針は、感染予防・再発防止対策及び感染症発生時の適切な対応など、事業所における感染予防対策体制を確立し、適切かつ安全で、質の高いサービスの提供を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>2．体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>（1）委員会の設置・運営</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>1　目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>事業所における感染症の発生や感染拡大を防止するために、感染対策委員会を設置する。感染対策委員会は、虐待防止委員会等の事業所の他の委員会と独立して設置・運営する。なお、他の会議体と一体的に開催することを妨げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>2　位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>代表取締役</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="C39" s="38" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="C41" s="38" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>感染対策委員会</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>虐待防止委員会</t>
+        </is>
+      </c>
+      <c r="D42" s="37" t="inlineStr">
+        <is>
+          <t>身体拘束適正化委員会</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="C43" s="38" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>サービス提供責任者</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>訪問介護員</t>
+        </is>
+      </c>
+      <c r="D44" s="37" t="inlineStr">
+        <is>
+          <t>事務職員</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="8" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>3　活動内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>感染対策委員会の主な活動内容は、以下の通りとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事業所の感染課題を明確にし、感染対策の方針・計画を定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染予防に関する決定事項や具体的対策を事業所全体に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事業所における感染に関する問題を把握し、問題意識を共有・解決する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者・職員の健康状態を把握する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染症が発生した場合、適切に対処するとともに、感染対策及び拡大防止の指揮を執る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・その他、感染関連の検討が必要な場合に、対処する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>4　委員会構成メンバー</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>感染対策委員会は、次のメンバーで構成する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・管理者（委員長）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス提供責任者（感染対策担当者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・訪問介護員の代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事務職員</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・必要に応じて、外部の感染対策の専門家（医師・看護師・保健所等）の助言を得る</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>5　運営方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>感染対策委員会は、おおむね6か月に1回以上（4月・10月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>会議の詳細（実施時間や内容、検討事項、開催方法等）は、感染対策委員会開催1週間前までに管理者より各メンバーへ連絡する。結果は記録し、全職員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="10" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
+        <is>
+          <t>（2）役割分担</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>各担当の役割分担は、以下の通りとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="39" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="39" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="39" t="inlineStr">
+        <is>
+          <t>事業所全体の管理、感染対策委員会の運営</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="40" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="48" customHeight="1">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>感染対策担当者
+感染対策の立案・指導
+利用者・職員の健康状態の把握</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="40" t="inlineStr">
+        <is>
+          <t>サービス提供責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t>訪問現場における感染対策の実施
+利用者の体調変化の報告</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="40" t="inlineStr">
+        <is>
+          <t>訪問介護員</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>委員会実施のための連絡・調整、記録の管理
+衛生用品の在庫管理</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="40" t="inlineStr">
+        <is>
+          <t>事務職員</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="36" t="inlineStr">
+        <is>
+          <t>（3）指針の整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>感染対策委員会は、感染に関する最新の情報を把握し、研修や訓練を通して課題を見つけ、定期的に指針を見直し、更新する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="10" customHeight="1"/>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="36" t="inlineStr">
+        <is>
+          <t>（4）研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>感染対策の基本的内容等の適切な知識を普及・啓発するとともに、本指針に基づいた衛生管理の徹底や衛生的な支援の励行を行うものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>指針に基づいた研修プログラムを作成し、全職員（登録ヘルパーを含む）を対象に定期的に年2回以上、かつ、新規採用時に感染対策研修を実施する。研修の企画、運営、実施記録の作成は、感染対策委員会が実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="39" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t>全職員</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="39" t="inlineStr">
+        <is>
+          <t>新規入職者</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="n"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="39" t="inlineStr">
+        <is>
+          <t>開催時期</t>
+        </is>
+      </c>
+      <c r="B82" s="40" t="inlineStr">
+        <is>
+          <t>5月・11月</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="40" t="inlineStr">
+        <is>
+          <t>入職時</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n"/>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="39" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="B83" s="40" t="inlineStr">
+        <is>
+          <t>感染予防対策と
+感染症発生時の対応方法</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="40" t="inlineStr">
+        <is>
+          <t>感染対策の重要性と
+標準予防策の理解</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>研修講師は、感染対策委員会が任命する。研修内容の詳細（開催日時、講師、方法、内容等）は、研修1か月前に、全職員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="10" customHeight="1"/>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="36" t="inlineStr">
+        <is>
+          <t>（5）訓練</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>感染者発生時において迅速に行動できるよう、発生時の対応を定めた本指針及び研修内容に基づき、全職員を対象に年2回以上の訓練（シミュレーション）を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="48" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>内容は、役割分担の確認や、感染対策をした上での訪問介護の演習（個人防護具の着脱等）などを実施するものとする。訓練方法は、机上訓練と実地訓練を組み合わせながら実施する。訓練の企画、運営、実施記録の作成は、感染対策委員会が実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>訓練内容の詳細（開催日時、実施方法、内容等）は、訓練1か月前に、全職員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="39" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B91" s="39" t="inlineStr">
+        <is>
+          <t>全職員</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="39" t="inlineStr">
+        <is>
+          <t>全職員</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="n"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="39" t="inlineStr">
+        <is>
+          <t>開催時期</t>
+        </is>
+      </c>
+      <c r="B92" s="40" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="40" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="A93" s="39" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="B93" s="40" t="inlineStr">
+        <is>
+          <t>感染対策マニュアルや
+感染症BCPを利用した行動確認</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="40" t="inlineStr">
+        <is>
+          <t>感染症発生時の対応訓練
+（個人防護具の着脱等）</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="n"/>
+    </row>
+    <row r="94" ht="8" customHeight="1"/>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="35" t="inlineStr">
+        <is>
+          <t>3．日常の支援にかかる感染管理（平常時の対策）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="36" t="inlineStr">
+        <is>
+          <t>（1）利用者の健康管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>主担当：サービス提供責任者（副担当：管理者）を中心に利用者の健康を管理するために必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　サービス開始前に、既往歴や感染症の有無について把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　訪問時に利用者の様子を観察し、体調の把握に努める</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　利用者の体調、様子などを、居宅介護支援事業所（ケアマネジャー）や家族と共有する方法を構築する</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　利用者・家族に対し、感染対策の方法を説明し、協力を依頼する</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　利用者の感染対策実施状況を把握し、不足している対策を支援する</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="36" t="inlineStr">
+        <is>
+          <t>（2）職員の健康管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に職員の健康を管理するために必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　入職時の感染症の既往やワクチン接種状況を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　定期健康診断の必要性を説明し、受診状況を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　訪問前に検温等を行い、職員の体調把握に努める</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　体調不良時の申告方法を周知し、申告しやすい環境を整える。発熱等の症状がある職員は訪問させない</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　職員へ感染対策の方法を教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6　職員の感染に対する知識を評価し、不足している部分に対し、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7　ワクチン接種の必要性を説明し、接種を推奨する</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　8　業務中に感染した場合の方針を明確にし、対応について準備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="36" t="inlineStr">
+        <is>
+          <t>（3）標準的な感染予防策</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>主担当：サービス提供責任者（副担当：管理者）を中心に、標準的な感染予防策の実施に必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>A．職員の感染予防策</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　訪問の前後及びケアの前後の手指衛生の実施状況（方法、タイミングなど）を評価し、適切な方法を教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　個人防護具（手袋・マスク・エプロン等）の使用状況（着用しているケアと着用状況、着脱方法など）を評価し、適切な方法を教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　食事介助時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　排泄介助・おむつ交換時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　入浴介助・清拭時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6　上記以外の支援時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="8" customHeight="1"/>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="26" t="inlineStr">
+        <is>
+          <t>B．利用者の感染予防策</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　食事前、排泄後の手洗い状況を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　手指を清潔に保つために必要な支援について検討し、実施する</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　居宅内で共用する物品（タオル・食器等）の使用状況を把握し、清潔な管理を助言する</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="8" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="26" t="inlineStr">
+        <is>
+          <t>C．その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　個人防護具・消毒液等の衛生用品を十分に確保し、管理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　訪問用の衛生用品セットを準備し、訪問介護員が常に携行できるようにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="8" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="36" t="inlineStr">
+        <is>
+          <t>（4）衛生管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="27" t="inlineStr">
+        <is>
+          <t>主担当：サービス提供責任者（副担当：管理者）を中心に、衛生管理に必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="26" t="inlineStr">
+        <is>
+          <t>A．環境整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　事業所内の整理整頓、清掃を計画的に実施し、実施状況を評価する</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　事業所及び利用者宅の換気の状況（方法や時間）を把握し、助言する</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　利用者宅での掃除援助において、トイレ・洗面所等の清掃を適切に行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　効果的な環境整備について、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="26" t="inlineStr">
+        <is>
+          <t>B．食品衛生（調理援助時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　食品の購入、保管状況（冷蔵庫内の期限切れ食品等）を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　調理工程の衛生状況（手洗い、加熱、まな板・包丁の使い分け等）を確認し、評価する</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　調理を行う訪問介護員の衛生状況を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　課題を検討し、対策を講じる</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　衛生的に調理できるよう、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="8" customHeight="1"/>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="26" t="inlineStr">
+        <is>
+          <t>C．血液・体液・排泄物等の処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　標準予防策について指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　ケアごとの標準予防策を策定し、周知する</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　嘔吐物・排泄物等の処理方法、処理状況を確認する。処理用品を訪問用セットに含める</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　使用済みのおむつ・手袋等は、利用者宅の廃棄ルールに従い、ビニール袋で密閉して処理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　適切な血液・体液・排泄物等の処理方法について、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="8" customHeight="1"/>
+    <row r="156" ht="26" customHeight="1">
+      <c r="A156" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ．発生時の対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="26" customHeight="1">
+      <c r="A157" s="35" t="inlineStr">
+        <is>
+          <t>1．発生状況の把握</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="27" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、感染症発生時の状況を把握するための必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　感染者及び感染疑い者（利用者・職員）の状況を把握し、情報を共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　事業所全体（訪問先の利用者を含む）の感染者及び感染疑い者の発生状況を調査し、把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　感染者等を訪問した訪問介護員及び訪問先を特定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="8" customHeight="1"/>
+    <row r="163" ht="26" customHeight="1">
+      <c r="A163" s="35" t="inlineStr">
+        <is>
+          <t>2．感染拡大の防止</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="32" customHeight="1">
+      <c r="A164" s="27" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、感染拡大防止のために必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="32" customHeight="1">
+      <c r="A165" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　感染者及び感染疑い者への訪問方法（訪問順を最後にする、担当者を限定する等）を検討し、周知、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　訪問介護員は、個人防護具を適切に着用し、感染者及び感染疑い者への支援方法を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="32" customHeight="1">
+      <c r="A167" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　感染状況を本人・家族へ説明し、感染対策（マスクの着用、手指衛生、換気など）の協力を依頼する</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　感染者及び感染疑い者と接触した関係者（職員、家族など）の体調を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　ウイルスや細菌に効果的な消毒薬を選定し、消毒を実施する</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6　職員の感染対策の状況を確認し、感染対策の徹底を促す</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7　訪問継続が困難な場合は、居宅介護支援事業所と連携し、サービス調整を行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="8" customHeight="1"/>
+    <row r="173" ht="26" customHeight="1">
+      <c r="A173" s="35" t="inlineStr">
+        <is>
+          <t>3．医療機関や保健所、行政関係機関との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="32" customHeight="1">
+      <c r="A174" s="27" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、必要な公的機関との連携について対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="26" t="inlineStr">
+        <is>
+          <t>A．医療機関との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　主治医へ感染者及び感染疑い者の状態を報告し、対応方法を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　受診の協力を依頼する</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　医療機関からの指示内容を事業所内で共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="8" customHeight="1"/>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="26" t="inlineStr">
+        <is>
+          <t>B．保健所との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　疾病の種類、状況により報告を検討する</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　感染者及び感染疑い者の状況を報告し、指示を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　保健所からの指導内容を正しく全職員に共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="8" customHeight="1"/>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="26" t="inlineStr">
+        <is>
+          <t>C．行政関係機関との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　大阪市への報告の必要性について検討する</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　感染者及び感染疑い者の状況を報告し、指示を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="8" customHeight="1"/>
+    <row r="189" ht="26" customHeight="1">
+      <c r="A189" s="35" t="inlineStr">
+        <is>
+          <t>4．関係者への連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="32" customHeight="1">
+      <c r="A190" s="27" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、関係先との情報共有や連携について対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　事業所内・法人内での情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　利用者家族との情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　居宅介護支援事業所（ケアマネジャー）との情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　利用者が利用している他のサービス事業所との情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="8" customHeight="1"/>
+    <row r="196" ht="26" customHeight="1">
+      <c r="A196" s="35" t="inlineStr">
+        <is>
+          <t>5．感染者発生後の支援（利用者、職員ともに）</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="32" customHeight="1">
+      <c r="A197" s="27" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、感染者の支援（心のケアなど）について対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　感染者及び感染疑い者の病状や予後を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　感染者及び関係者の精神的ケアを行う体制を構築する</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　感染症からの回復後のサービス再開について、居宅介護支援事業所と調整する</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="8" customHeight="1"/>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="26" t="inlineStr">
+        <is>
+          <t>＜変更・廃止手続＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="27" t="inlineStr">
+        <is>
+          <t>本指針の変更および廃止は、感染対策委員会の審議を経て、代表取締役が決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="8" customHeight="1"/>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="26" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="27" t="inlineStr">
+        <is>
+          <t>本指針は、令和8年2月1日から適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="41" t="inlineStr">
+        <is>
+          <t>以上</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="157">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="A166:E166"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A207:E207"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A182:E182"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="A168:E168"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A192:E192"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A185:E185"/>
+    <mergeCell ref="A194:E194"/>
+    <mergeCell ref="A203:E203"/>
+    <mergeCell ref="A181:E181"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A171:E171"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A173:E173"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A157:E157"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A196:E196"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A205:E205"/>
+    <mergeCell ref="A183:E183"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A198:E198"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A175:E175"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A159:E159"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A200:E200"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A161:E161"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A186:E186"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A197:E197"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A187:E187"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A174:E174"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A189:E189"/>
+    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="A160:E160"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A206:E206"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A199:E199"/>
+    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A191:E191"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A178:E178"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A164:E164"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A154:E154"/>
+    <mergeCell ref="A163:E163"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A180:E180"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A190:E190"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A143:E143"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　感染症対策指針</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>
@@ -8010,96 +9529,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="35" t="inlineStr">
+      <c r="B1" s="42" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>法人名</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="43" t="inlineStr">
         <is>
           <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>ええかいご → いいかいご（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>管理者・サービス提供責任者等</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>要入力</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>なし（すべて入力済み）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>コメント付きセル</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>説明年月日・利用者欄</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>新しく使えるよう空欄にしています</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>元の資料</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
         </is>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -9,21 +9,22 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重要事項説明書" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="契約書" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人情報使用同意書" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="総合事業契約書" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人情報使用同意書" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3611,6 +3612,846 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E146"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>休暇規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に付与される休暇に関する事項を定め、労働基準法その他関係法令を遵守しつつ、従業員の心身の健康保持と円滑な業務運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、嘱託社員、短時間勤務者、アルバイト等については、就業形態に応じて別途定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>第2章　年次有給休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>（付与要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>第3条　会社は、継続勤務6か月を経過し、その期間の全労働日の8割以上出勤した従業員に対し、10日の年次有給休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>（取得方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>（時季変更権）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>（時間単位年休）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>（計画的付与）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>（年5日の取得義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>（有効期限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="28" t="inlineStr"/>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="12" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="12" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>第3章　特別休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="26" t="inlineStr">
+        <is>
+          <t>（慶弔休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>1　本人の結婚：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>2　子女の結婚：2日</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>3　配偶者の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>4　父母・子の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>6　その他会社が必要と認めた場合：別途定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
+          <t>（産前産後休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="8" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>（育児休業・介護休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="26" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇・介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>（病気休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>（公務・公用休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>（感染症予防に伴う休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>（生理休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>（育児時間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>（母性健康管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="26" t="inlineStr">
+        <is>
+          <t>（誕生日休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="8" customHeight="1"/>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>（その他の特別休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="8" customHeight="1"/>
+    <row r="114" ht="8" customHeight="1">
+      <c r="A114" s="28" t="inlineStr"/>
+      <c r="B114" s="12" t="n"/>
+      <c r="C114" s="12" t="n"/>
+      <c r="D114" s="12" t="n"/>
+      <c r="E114" s="12" t="n"/>
+    </row>
+    <row r="115" ht="10" customHeight="1"/>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="25" t="inlineStr">
+        <is>
+          <t>第4章　手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>（申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="26" t="inlineStr">
+        <is>
+          <t>（診断書等の提出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>1　私傷病により連続して3日以上欠勤するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>2　休職を申請するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="27" t="inlineStr">
+        <is>
+          <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="27" t="inlineStr">
+        <is>
+          <t>5　会社が安全衛生管理上必要と認めたとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="28" t="inlineStr"/>
+      <c r="B133" s="12" t="n"/>
+      <c r="C133" s="12" t="n"/>
+      <c r="D133" s="12" t="n"/>
+      <c r="E133" s="12" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="25" t="inlineStr">
+        <is>
+          <t>第5章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="26" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="26" t="inlineStr">
+        <is>
+          <t>（休暇中の待遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="32" customHeight="1">
+      <c r="A140" s="27" t="inlineStr">
+        <is>
+          <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="8" customHeight="1">
+      <c r="A142" s="28" t="inlineStr"/>
+      <c r="B142" s="12" t="n"/>
+      <c r="C142" s="12" t="n"/>
+      <c r="D142" s="12" t="n"/>
+      <c r="E142" s="12" t="n"/>
+    </row>
+    <row r="143" ht="10" customHeight="1"/>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="94">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　休暇規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4776,7 +5617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5187,7 +6028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5948,7 +6789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6658,7 +7499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7340,7 +8181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8027,7 +8868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9515,7 +10356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10526,6 +11367,799 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19.5" customWidth="1" min="2" max="2"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="19.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業第1号事業契約書</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>利用者　　　　　　　　　　　　　　様（以下「利用者」という。）と事業者　株式会社dhpケアマネジメント（以下「事業者」という。）は、事業者が提供するサービスの利用等について、次のとおり契約を締結します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1 契約の目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>事業者は、介護保険法（平成9年法律第123号）その他関係法令及びこの契約書に従い、利用者が可能な限り居宅においてその有する能力に応じ、自立した日常生活を営むことができるよう、次のサービスを提供します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　第1号訪問事業　　介護予防訪問介護相当サービス（「契約書別紙（兼重要事項説明書）」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2 契約期間</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>(1) この契約の期間は、次のとおりとします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　令和　　年　　月　　日　～　令和　　年　　月　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>(2) 上記契約期間満了日までに利用者から契約更新しない旨の申出がない場合、本契約は自動的に更新されるものとします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>3 個別サービス計画の作成及び変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>(1) 事業者は、必要に応じて利用者の日常生活全般の状況、心身の状況及び希望を踏まえ、利用者の介護予防サービス計画書又は介護予防ケアマネジメントケアプラン（以下、「介護予防ケアプラン」という。）の内容に沿って、サービスの目標及び目標を達成するための具体的なサービス内容等を記載した個別サービス計画を作成します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>(2) 個別サービス計画の作成に当たっては、事業者はその内容を利用者に説明して同意を得て、交付します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>(3) 事業者は、計画実施状況の把握を適切に行い、一定期間ごとに、目標達成の状況等を記載した記録を作成し、利用者に説明の上、交付します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>4 提供するサービスの内容及びその変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>(1) 事業者が提供するサービスのうち、利用者が利用するサービス内容、利用回数及び利用料は、「契約書別紙（兼重要事項説明書）」のとおりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>(2) 利用者は、いつでもサービスの内容を変更するよう申し出ることができます。この申出があった場合、当該変更が介護予防ケアプランの範囲内で可能であり、1に規定する契約の目的に反するなど変更を拒む正当な理由がない限り、速やかにサービスの内容を変更します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>(3) 事業者は、利用者が介護予防ケアプランの変更を希望する場合は、速やかに地域包括支援センターに連絡するなど必要な援助を行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>(4) 事業者は、提供するサービスのうち、介護保険の適用を受けないものがある場合には、そのサービスの内容及び利用料を具体的に説明し、利用者の同意を得ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>5 利用料等の支払</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>(1) 利用者は、事業者からサービスの提供を受けたときは、「契約書別紙（兼重要事項説明書）」の記載に従い、事業者に対し、利用者負担金を支払います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>(2) 利用料の請求や支払方法は、「契約書別紙（兼重要事項説明書）」のとおりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>(3) 利用者が、「契約書別紙（兼重要事項説明書）」に記載の期日までにサービス利用の中止を申し入れなかった場合、利用者は事業者へキャンセル料を支払うものとします。ただし、体調や容体の急変など、やむを得ない事情がある場合は、キャンセル料は不要とします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>6 利用料の変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>事業者は、介護保険法その他関係法令の改正により、利用料の利用者負担金に変更が生じた場合は、利用者に対し速やかに変更の時期及び変更後の金額を説明の上、変更後の利用者負担金を請求することができるものとします。ただし、利用者は、この変更に同意することができない場合には、本契約を解約することができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>7 利用料の滞納</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>(1) 利用者が正当な理由なく事業者に支払うべき利用者負担金を2か月以上滞納した場合は、事業者は、利用者に対し、1か月以上の猶予期間を設けた上で支払期限を定め、当該期限までに滞納額の全額の支払がないときはこの契約を解約する旨の催告をすることができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>(2) 事業者は、7の(1)の催告をした場合には、担当の地域包括支援センター及び関係市町村と連絡を取り、解約後も利用者の健康や生命に支障のないよう、必要な措置を講じます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>(3) 事業者は、7の(2)の措置を講じた上で、利用者が7の(1)の期間内に滞納額を支払わなかったときは、文書をもって本契約を解約することができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>8 利用者の解約権</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>(1) 利用者は、7日以上の予告期間を設けることにより、事業者に対しいつでもこの契約の解約を申し出ることができます。この場合において、予告期間満了日に契約は解約されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>(2) 利用者は、次のいずれかに該当する場合は、8の(1)の規定にかかわらず、予告期間を設けることなく直ちにこの契約を解約できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ア　事業者が、正当な理由なく本契約に定めるサービスを提供せず、利用者の請求にもかかわらず、これを提供しようとしない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　イ　事業者が、12に定める守秘義務に違反した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ウ　事業者が、利用者の身体・財産・名誉等を傷つけ、又は著しい不信行為を行うなど、本契約を継続しがたい重大な事由が認められる場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>9 事業者の解約権</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>(1) 事業者は、次のいずれかに該当する場合は、文書により2週間以上の予告期間をもって、この契約を解約することができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ア　利用者が故意に法令違反その他著しく常識を逸脱する行為をなし、事業者の再三の申し入れにもかかわらず改善の見込みがなく、本契約の目的を達することが著しく困難となった場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　イ　利用者が事業者の通常の事業の実施地域外に転居し、事業者においてサービスの提供の継続が困難であると見込まれる場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>(2) 事業者は、9の(1)によりこの契約を解約する場合には、担当の地域包括支援センター及び必要に応じて関係市町村に連絡を取り、解約後も利用者の健康や生命に支障のないよう、必要な措置を講じます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>10 契約の終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>次のいずれかに該当する場合は、この契約は終了します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>(1) 2の(2)の規定により利用者から契約更新しない旨の申出があり、契約期間が満了した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>(2) 8の(1)の規定により利用者から解約の意思表示がなされ、予告期間が満了した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>(3) 6又は8の(2)の規定により利用者から解約の意思表示がなされた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>(4) 7の規定により事業者から解約の意思表示がなされた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>(5) 9の規定により事業者から解約の意思表示がなされ、予告期間が満了した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>(6) 利用者が介護保険施設へ入所した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>(7) 利用者が介護予防特定施設入居者生活介護、介護予防認知症対応型共同生活介護、介護予防小規模多機能型居宅介護又は看護小規模多機能型居宅介護を受けることとなった場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>(8) 利用者の要介護状態区分が自立又は要介護となった場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>(9) 利用者が死亡した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>11 損害賠償</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>(1) 事業者は、サービスの提供にあたり、利用者又は利用者の家族の生命・身体・財産に損害が発生した場合は、速やかに利用者又は利用者の家族に対して損害を賠償します。ただし、当該損害について事業者の責任を問えない場合はこの限りではありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>(2) 前項の義務履行を確保するため、事業者は損害賠償保険に加入します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>(3) 利用者又は利用者の家族に重大な過失がある場合、賠償額を減額することができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>12 守秘義務</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>(1) 事業者及び事業者の従事者は、サービスの提供にあたって知り得た利用者又は利用者の家族の秘密及び個人情報について、正当な理由がない限り、契約中及び契約終了後においても、第三者には漏らしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>(2) 事業者は、事業者の従業員が退職後、在職中に知り得た利用者又は利用者の家族の秘密及び個人情報を漏らすことがないよう必要な処置を講じます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>(3) 事業者は、利用者及び利用者の家族の個人情報について、介護保険法第23条の規定によるもののほか、利用者の介護予防ケアプラン立案のためのサービス担当者会議並びに地域包括支援センター及び介護予防サービス事業者等との連絡調整において必要な場合に限り、必要最小限の範囲内で使用します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>(4) 12の(1)の規定にかかわらず、事業者は、高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律（平成17年法律第124号）に定める通報ができるものとし、その場合、事業者は秘密保持義務違反の責任を負わないものとします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>13 苦情処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>(1) 利用者又は利用者の家族は、提供されたサービスに苦情がある場合は、「契約書別紙（兼重要事項説明書）」に記載された事業者の相談窓口及び関係機関に対して、いつでも苦情を申し立てることができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>(2) 事業者は、提供したサービスについて、利用者又は利用者の家族から苦情の申出があった場合は、迅速かつ適切に対処し、サービスの向上及び改善に努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>(3) 事業者は、利用者が苦情申立を行った場合、これを理由としていかなる不利益な扱いもいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>14 サービス内容等の記録の作成及び保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>(1) 事業者は、サービスの提供に関する記録を整備し、完結の日から5年間保存します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="45" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>(2) 利用者及び利用者の後見人（必要に応じ、利用者の家族を含む。）は、事業者に対し、いつでも前項の記録の閲覧及び複写を求めることができます。ただし、複写に際しては、事業者は利用者に対して、実費相当額を請求できるものとします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="45" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>(3) 事業者は、契約の終了にあたって必要があると認められる場合は、利用者の同意を得た上で、利用者の指定する他の居宅介護支援事業者等へ、14の(1)の記録の写しを交付することができるものとします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>15 契約外条項</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>(1) 本契約に定めのない事項については、介護保険法その他関係法令の定めるところを尊重し、利用者及び事業者の協議により定めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>以上のとおり、介護予防・日常生活支援総合事業第1号事業に関する契約を締結します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>上記契約を証するため、本書2通を作成し、利用者及び事業者の双方が記名・押印の上、それぞれ1部ずつ保有します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>契約締結日</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>令和　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="n"/>
+      <c r="D90" s="12" t="n"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>（利用者）私は、この契約内容に同意し、サービスの利用を申し込みます。また、12の(3)に定める利用者の個人情報の使用について、同意します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr"/>
+      <c r="C93" s="12" t="n"/>
+      <c r="D93" s="12" t="n"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr"/>
+      <c r="C94" s="12" t="n"/>
+      <c r="D94" s="12" t="n"/>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>（代理人）私は、利用者本人の契約の意思を確認の上、本人に代わり、上記署名を行いました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>署名代行者 住所</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr"/>
+      <c r="C97" s="12" t="n"/>
+      <c r="D97" s="12" t="n"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr"/>
+      <c r="C98" s="12" t="n"/>
+      <c r="D98" s="12" t="n"/>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>（事業者）私は、利用者の申込みを受託し、この契約書に定める各種サービスを、誠実に責任をもって行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>事業者 所在地</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>〒541-0058 大阪市中央区南久宝寺町四丁目5番17号 アップウェル船場 2F</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n"/>
+      <c r="D101" s="12" t="n"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>事業者名</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="n"/>
+      <c r="D102" s="12" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>代表者職・氏名</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>代表取締役　吉田 駿成</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="n"/>
+      <c r="D103" s="12" t="n"/>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>（立会人）私は、（※利用者との続柄）として、この契約に立ち会いました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr"/>
+      <c r="C106" s="12" t="n"/>
+      <c r="D106" s="12" t="n"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr"/>
+      <c r="C107" s="12" t="n"/>
+      <c r="D107" s="12" t="n"/>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>続柄</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr"/>
+      <c r="C108" s="12" t="n"/>
+      <c r="D108" s="12" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="86">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="88" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10768,7 +12402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11290,7 +12924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12056,7 +13690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12675,7 +14309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13338,7 +14972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13800,844 +15434,4 @@
     <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E146"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1"/>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>休暇規程</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>施行　令和8年2月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>第1章　総則</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>（目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に付与される休暇に関する事項を定め、労働基準法その他関係法令を遵守しつつ、従業員の心身の健康保持と円滑な業務運営を図ることを目的とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、嘱託社員、短時間勤務者、アルバイト等については、就業形態に応じて別途定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="8" customHeight="1">
-      <c r="A33" s="28" t="inlineStr"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="10" customHeight="1"/>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>第2章　年次有給休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>（付与要件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>第3条　会社は、継続勤務6か月を経過し、その期間の全労働日の8割以上出勤した従業員に対し、10日の年次有給休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
-        <is>
-          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
-        <is>
-          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="26" t="inlineStr">
-        <is>
-          <t>（取得方法）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="8" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>（時季変更権）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>（時間単位年休）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t>（計画的付与）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="8" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="26" t="inlineStr">
-        <is>
-          <t>（年5日の取得義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="8" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="26" t="inlineStr">
-        <is>
-          <t>（有効期限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
-        <is>
-          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="8" customHeight="1"/>
-    <row r="63" ht="8" customHeight="1">
-      <c r="A63" s="28" t="inlineStr"/>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="12" t="n"/>
-    </row>
-    <row r="64" ht="10" customHeight="1"/>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="25" t="inlineStr">
-        <is>
-          <t>第3章　特別休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="26" t="inlineStr">
-        <is>
-          <t>（慶弔休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="27" t="inlineStr">
-        <is>
-          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="27" t="inlineStr">
-        <is>
-          <t>1　本人の結婚：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="27" t="inlineStr">
-        <is>
-          <t>2　子女の結婚：2日</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="27" t="inlineStr">
-        <is>
-          <t>3　配偶者の死亡：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>4　父母・子の死亡：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
-        <is>
-          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
-        <is>
-          <t>6　その他会社が必要と認めた場合：別途定める</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="27" t="inlineStr">
-        <is>
-          <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="8" customHeight="1"/>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="26" t="inlineStr">
-        <is>
-          <t>（産前産後休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="27" t="inlineStr">
-        <is>
-          <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="8" customHeight="1"/>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="26" t="inlineStr">
-        <is>
-          <t>（育児休業・介護休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="27" t="inlineStr">
-        <is>
-          <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="8" customHeight="1"/>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="26" t="inlineStr">
-        <is>
-          <t>（子の看護等休暇・介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="27" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="27" t="inlineStr">
-        <is>
-          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="27" t="inlineStr">
-        <is>
-          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="26" t="inlineStr">
-        <is>
-          <t>（病気休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
-        <is>
-          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="8" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="26" t="inlineStr">
-        <is>
-          <t>（公務・公用休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="27" t="inlineStr">
-        <is>
-          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="26" t="inlineStr">
-        <is>
-          <t>（感染症予防に伴う休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="27" t="inlineStr">
-        <is>
-          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="27" t="inlineStr">
-        <is>
-          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>（生理休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="27" t="inlineStr">
-        <is>
-          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="8" customHeight="1"/>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="26" t="inlineStr">
-        <is>
-          <t>（育児時間）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="32" customHeight="1">
-      <c r="A101" s="27" t="inlineStr">
-        <is>
-          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="8" customHeight="1"/>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="26" t="inlineStr">
-        <is>
-          <t>（母性健康管理）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="27" t="inlineStr">
-        <is>
-          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="8" customHeight="1"/>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="26" t="inlineStr">
-        <is>
-          <t>（誕生日休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="27" t="inlineStr">
-        <is>
-          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="27" t="inlineStr">
-        <is>
-          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="27" t="inlineStr">
-        <is>
-          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="8" customHeight="1"/>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="26" t="inlineStr">
-        <is>
-          <t>（その他の特別休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="27" t="inlineStr">
-        <is>
-          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="8" customHeight="1"/>
-    <row r="114" ht="8" customHeight="1">
-      <c r="A114" s="28" t="inlineStr"/>
-      <c r="B114" s="12" t="n"/>
-      <c r="C114" s="12" t="n"/>
-      <c r="D114" s="12" t="n"/>
-      <c r="E114" s="12" t="n"/>
-    </row>
-    <row r="115" ht="10" customHeight="1"/>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="25" t="inlineStr">
-        <is>
-          <t>第4章　手続</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="26" t="inlineStr">
-        <is>
-          <t>（申請手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="27" t="inlineStr">
-        <is>
-          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="26" t="inlineStr">
-        <is>
-          <t>（診断書等の提出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="27" t="inlineStr">
-        <is>
-          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="27" t="inlineStr">
-        <is>
-          <t>1　私傷病により連続して3日以上欠勤するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="27" t="inlineStr">
-        <is>
-          <t>2　休職を申請するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="27" t="inlineStr">
-        <is>
-          <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="27" t="inlineStr">
-        <is>
-          <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="27" t="inlineStr">
-        <is>
-          <t>5　会社が安全衛生管理上必要と認めたとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="27" t="inlineStr">
-        <is>
-          <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="27" t="inlineStr">
-        <is>
-          <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="8" customHeight="1"/>
-    <row r="133" ht="8" customHeight="1">
-      <c r="A133" s="28" t="inlineStr"/>
-      <c r="B133" s="12" t="n"/>
-      <c r="C133" s="12" t="n"/>
-      <c r="D133" s="12" t="n"/>
-      <c r="E133" s="12" t="n"/>
-    </row>
-    <row r="134" ht="10" customHeight="1"/>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="25" t="inlineStr">
-        <is>
-          <t>第5章　その他</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="26" t="inlineStr">
-        <is>
-          <t>（不利益取扱い禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="27" t="inlineStr">
-        <is>
-          <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="8" customHeight="1"/>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="26" t="inlineStr">
-        <is>
-          <t>（休暇中の待遇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="32" customHeight="1">
-      <c r="A140" s="27" t="inlineStr">
-        <is>
-          <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="8" customHeight="1"/>
-    <row r="142" ht="8" customHeight="1">
-      <c r="A142" s="28" t="inlineStr"/>
-      <c r="B142" s="12" t="n"/>
-      <c r="C142" s="12" t="n"/>
-      <c r="D142" s="12" t="n"/>
-      <c r="E142" s="12" t="n"/>
-    </row>
-    <row r="143" ht="10" customHeight="1"/>
-    <row r="144" ht="30" customHeight="1">
-      <c r="A144" s="25" t="inlineStr">
-        <is>
-          <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="27" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="27" t="inlineStr">
-        <is>
-          <t>2　本規程は令和8年2月1日から施行する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="94">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A142:E142"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A136:E136"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="A131:E131"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A130:E130"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A120:E120"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A146:E146"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A135:E135"/>
-    <mergeCell ref="A144:E144"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A127:E127"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A145:E145"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A111:E111"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　休暇規程</oddHeader>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
 </file>
--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -9186,7 +9186,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="27" t="inlineStr">
         <is>
-          <t>感染対策委員会は、おおむね6か月に1回以上（4月・10月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
+          <t>感染対策委員会は、おおむね6か月に1回以上（6月・11月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="B82" s="40" t="inlineStr">
         <is>
-          <t>5月・11月</t>
+          <t>6月・11月</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="B92" s="40" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="C92" s="4" t="n"/>

--- a/output/いいかいご_契約書類一式.xlsx
+++ b/output/いいかいご_契約書類一式.xlsx
@@ -9,22 +9,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重要事項説明書" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="契約書" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="総合事業契約書" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人情報使用同意書" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人情報使用同意書" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更点・要入力" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -343,11 +342,6 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="B22" authorId="0" shapeId="0">
-      <text>
-        <t>原本の「指定本文介護」は「指定訪問介護」の誤字と思われます（原本のまま）</t>
-      </text>
-    </comment>
     <comment ref="B188" authorId="0" shapeId="0">
       <text>
         <t>旧法人の加入内容のまま。要確認</t>
@@ -852,7 +846,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="75" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>事業の目的</t>
@@ -860,7 +854,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>適正な運営を確保するために必要な人員及び運営管理に関する事項を定め、要介護状態（介護予防にあっては要支援状態）にある利用者に対し、指定訪問介護［指定介護予防介護訪問介護］の円滑な運営管理を図るとともに、利用者の意思及び人格を尊重し、利用者の立場にたった適切な指定本文介護［指定介護予防介護訪問介護］の提供を確保することを目的とする。</t>
+          <t>適正な運営を確保するために必要な人員及び運営管理に関する事項を定め、要介護状態にある利用者に対し、指定訪問介護の円滑な運営管理を図るとともに、利用者の意思及び人格を尊重し、利用者の立場にたった適切な指定訪問介護の提供を確保することを目的とする。</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -3612,846 +3606,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1"/>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>休暇規程</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>施行　令和8年2月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>第1章　総則</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>（目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に付与される休暇に関する事項を定め、労働基準法その他関係法令を遵守しつつ、従業員の心身の健康保持と円滑な業務運営を図ることを目的とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、嘱託社員、短時間勤務者、アルバイト等については、就業形態に応じて別途定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="8" customHeight="1">
-      <c r="A33" s="28" t="inlineStr"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="10" customHeight="1"/>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>第2章　年次有給休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>（付与要件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>第3条　会社は、継続勤務6か月を経過し、その期間の全労働日の8割以上出勤した従業員に対し、10日の年次有給休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
-        <is>
-          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
-        <is>
-          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="26" t="inlineStr">
-        <is>
-          <t>（取得方法）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="8" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>（時季変更権）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>（時間単位年休）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t>（計画的付与）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="8" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="26" t="inlineStr">
-        <is>
-          <t>（年5日の取得義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="8" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="26" t="inlineStr">
-        <is>
-          <t>（有効期限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
-        <is>
-          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="8" customHeight="1"/>
-    <row r="63" ht="8" customHeight="1">
-      <c r="A63" s="28" t="inlineStr"/>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="12" t="n"/>
-    </row>
-    <row r="64" ht="10" customHeight="1"/>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="25" t="inlineStr">
-        <is>
-          <t>第3章　特別休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="26" t="inlineStr">
-        <is>
-          <t>（慶弔休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="27" t="inlineStr">
-        <is>
-          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="27" t="inlineStr">
-        <is>
-          <t>1　本人の結婚：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="27" t="inlineStr">
-        <is>
-          <t>2　子女の結婚：2日</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="27" t="inlineStr">
-        <is>
-          <t>3　配偶者の死亡：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>4　父母・子の死亡：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
-        <is>
-          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
-        <is>
-          <t>6　その他会社が必要と認めた場合：別途定める</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="27" t="inlineStr">
-        <is>
-          <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="8" customHeight="1"/>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="26" t="inlineStr">
-        <is>
-          <t>（産前産後休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="27" t="inlineStr">
-        <is>
-          <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="8" customHeight="1"/>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="26" t="inlineStr">
-        <is>
-          <t>（育児休業・介護休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="27" t="inlineStr">
-        <is>
-          <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="8" customHeight="1"/>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="26" t="inlineStr">
-        <is>
-          <t>（子の看護等休暇・介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="27" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="27" t="inlineStr">
-        <is>
-          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="27" t="inlineStr">
-        <is>
-          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="26" t="inlineStr">
-        <is>
-          <t>（病気休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
-        <is>
-          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="8" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="26" t="inlineStr">
-        <is>
-          <t>（公務・公用休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="27" t="inlineStr">
-        <is>
-          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="26" t="inlineStr">
-        <is>
-          <t>（感染症予防に伴う休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="27" t="inlineStr">
-        <is>
-          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="27" t="inlineStr">
-        <is>
-          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>（生理休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="27" t="inlineStr">
-        <is>
-          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="8" customHeight="1"/>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="26" t="inlineStr">
-        <is>
-          <t>（育児時間）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="32" customHeight="1">
-      <c r="A101" s="27" t="inlineStr">
-        <is>
-          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="8" customHeight="1"/>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="26" t="inlineStr">
-        <is>
-          <t>（母性健康管理）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="27" t="inlineStr">
-        <is>
-          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="8" customHeight="1"/>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="26" t="inlineStr">
-        <is>
-          <t>（誕生日休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="27" t="inlineStr">
-        <is>
-          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="27" t="inlineStr">
-        <is>
-          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="27" t="inlineStr">
-        <is>
-          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="8" customHeight="1"/>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="26" t="inlineStr">
-        <is>
-          <t>（その他の特別休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="27" t="inlineStr">
-        <is>
-          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="8" customHeight="1"/>
-    <row r="114" ht="8" customHeight="1">
-      <c r="A114" s="28" t="inlineStr"/>
-      <c r="B114" s="12" t="n"/>
-      <c r="C114" s="12" t="n"/>
-      <c r="D114" s="12" t="n"/>
-      <c r="E114" s="12" t="n"/>
-    </row>
-    <row r="115" ht="10" customHeight="1"/>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="25" t="inlineStr">
-        <is>
-          <t>第4章　手続</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="26" t="inlineStr">
-        <is>
-          <t>（申請手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="27" t="inlineStr">
-        <is>
-          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="26" t="inlineStr">
-        <is>
-          <t>（診断書等の提出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="27" t="inlineStr">
-        <is>
-          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="27" t="inlineStr">
-        <is>
-          <t>1　私傷病により連続して3日以上欠勤するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="27" t="inlineStr">
-        <is>
-          <t>2　休職を申請するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="27" t="inlineStr">
-        <is>
-          <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="27" t="inlineStr">
-        <is>
-          <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="27" t="inlineStr">
-        <is>
-          <t>5　会社が安全衛生管理上必要と認めたとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="27" t="inlineStr">
-        <is>
-          <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="27" t="inlineStr">
-        <is>
-          <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="8" customHeight="1"/>
-    <row r="133" ht="8" customHeight="1">
-      <c r="A133" s="28" t="inlineStr"/>
-      <c r="B133" s="12" t="n"/>
-      <c r="C133" s="12" t="n"/>
-      <c r="D133" s="12" t="n"/>
-      <c r="E133" s="12" t="n"/>
-    </row>
-    <row r="134" ht="10" customHeight="1"/>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="25" t="inlineStr">
-        <is>
-          <t>第5章　その他</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="26" t="inlineStr">
-        <is>
-          <t>（不利益取扱い禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="27" t="inlineStr">
-        <is>
-          <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="8" customHeight="1"/>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="26" t="inlineStr">
-        <is>
-          <t>（休暇中の待遇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="32" customHeight="1">
-      <c r="A140" s="27" t="inlineStr">
-        <is>
-          <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="8" customHeight="1"/>
-    <row r="142" ht="8" customHeight="1">
-      <c r="A142" s="28" t="inlineStr"/>
-      <c r="B142" s="12" t="n"/>
-      <c r="C142" s="12" t="n"/>
-      <c r="D142" s="12" t="n"/>
-      <c r="E142" s="12" t="n"/>
-    </row>
-    <row r="143" ht="10" customHeight="1"/>
-    <row r="144" ht="30" customHeight="1">
-      <c r="A144" s="25" t="inlineStr">
-        <is>
-          <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="27" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="27" t="inlineStr">
-        <is>
-          <t>2　本規程は令和8年2月1日から施行する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="94">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A142:E142"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A136:E136"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="A131:E131"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A130:E130"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A120:E120"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A146:E146"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A135:E135"/>
-    <mergeCell ref="A144:E144"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A127:E127"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A145:E145"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A111:E111"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　休暇規程</oddHeader>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5617,7 +4771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6028,7 +5182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6789,7 +5943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7499,7 +6653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8181,7 +7335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8868,7 +8022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10356,7 +9510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10538,7 +9692,7 @@
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>本契約の有効期間は、本書に記載する契約開始年月日から始まり、利用者の要介護（支援）認定の有効期間満了日までとします。但し、契約期間満了の30日前までに利用者から文書による契約終了の申し入れがない場合には、本契約は更に同じ条件で更新されるものとし、以後も同様とします。</t>
+          <t>本契約の有効期間は、本書に記載する契約開始年月日から始まり、利用者の要介護認定の有効期間満了日までとします。但し、契約期間満了の30日前までに利用者から文書による契約終了の申し入れがない場合には、本契約は更に同じ条件で更新されるものとし、以後も同様とします。</t>
         </is>
       </c>
     </row>
@@ -11367,799 +10521,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="19.5" customWidth="1" min="2" max="2"/>
-    <col width="19.5" customWidth="1" min="3" max="3"/>
-    <col width="19.5" customWidth="1" min="4" max="4"/>
-    <col width="19.5" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>介護予防・日常生活支援総合事業第1号事業契約書</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>利用者　　　　　　　　　　　　　　様（以下「利用者」という。）と事業者　株式会社dhpケアマネジメント（以下「事業者」という。）は、事業者が提供するサービスの利用等について、次のとおり契約を締結します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>1 契約の目的</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>事業者は、介護保険法（平成9年法律第123号）その他関係法令及びこの契約書に従い、利用者が可能な限り居宅においてその有する能力に応じ、自立した日常生活を営むことができるよう、次のサービスを提供します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　第1号訪問事業　　介護予防訪問介護相当サービス（「契約書別紙（兼重要事項説明書）」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2 契約期間</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>(1) この契約の期間は、次のとおりとします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　令和　　年　　月　　日　～　令和　　年　　月　　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>(2) 上記契約期間満了日までに利用者から契約更新しない旨の申出がない場合、本契約は自動的に更新されるものとします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>3 個別サービス計画の作成及び変更</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>(1) 事業者は、必要に応じて利用者の日常生活全般の状況、心身の状況及び希望を踏まえ、利用者の介護予防サービス計画書又は介護予防ケアマネジメントケアプラン（以下、「介護予防ケアプラン」という。）の内容に沿って、サービスの目標及び目標を達成するための具体的なサービス内容等を記載した個別サービス計画を作成します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>(2) 個別サービス計画の作成に当たっては、事業者はその内容を利用者に説明して同意を得て、交付します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>(3) 事業者は、計画実施状況の把握を適切に行い、一定期間ごとに、目標達成の状況等を記載した記録を作成し、利用者に説明の上、交付します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>4 提供するサービスの内容及びその変更</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>(1) 事業者が提供するサービスのうち、利用者が利用するサービス内容、利用回数及び利用料は、「契約書別紙（兼重要事項説明書）」のとおりです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>(2) 利用者は、いつでもサービスの内容を変更するよう申し出ることができます。この申出があった場合、当該変更が介護予防ケアプランの範囲内で可能であり、1に規定する契約の目的に反するなど変更を拒む正当な理由がない限り、速やかにサービスの内容を変更します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>(3) 事業者は、利用者が介護予防ケアプランの変更を希望する場合は、速やかに地域包括支援センターに連絡するなど必要な援助を行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>(4) 事業者は、提供するサービスのうち、介護保険の適用を受けないものがある場合には、そのサービスの内容及び利用料を具体的に説明し、利用者の同意を得ます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>5 利用料等の支払</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>(1) 利用者は、事業者からサービスの提供を受けたときは、「契約書別紙（兼重要事項説明書）」の記載に従い、事業者に対し、利用者負担金を支払います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>(2) 利用料の請求や支払方法は、「契約書別紙（兼重要事項説明書）」のとおりです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>(3) 利用者が、「契約書別紙（兼重要事項説明書）」に記載の期日までにサービス利用の中止を申し入れなかった場合、利用者は事業者へキャンセル料を支払うものとします。ただし、体調や容体の急変など、やむを得ない事情がある場合は、キャンセル料は不要とします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>6 利用料の変更</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>事業者は、介護保険法その他関係法令の改正により、利用料の利用者負担金に変更が生じた場合は、利用者に対し速やかに変更の時期及び変更後の金額を説明の上、変更後の利用者負担金を請求することができるものとします。ただし、利用者は、この変更に同意することができない場合には、本契約を解約することができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>7 利用料の滞納</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>(1) 利用者が正当な理由なく事業者に支払うべき利用者負担金を2か月以上滞納した場合は、事業者は、利用者に対し、1か月以上の猶予期間を設けた上で支払期限を定め、当該期限までに滞納額の全額の支払がないときはこの契約を解約する旨の催告をすることができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>(2) 事業者は、7の(1)の催告をした場合には、担当の地域包括支援センター及び関係市町村と連絡を取り、解約後も利用者の健康や生命に支障のないよう、必要な措置を講じます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>(3) 事業者は、7の(2)の措置を講じた上で、利用者が7の(1)の期間内に滞納額を支払わなかったときは、文書をもって本契約を解約することができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>8 利用者の解約権</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>(1) 利用者は、7日以上の予告期間を設けることにより、事業者に対しいつでもこの契約の解約を申し出ることができます。この場合において、予告期間満了日に契約は解約されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>(2) 利用者は、次のいずれかに該当する場合は、8の(1)の規定にかかわらず、予告期間を設けることなく直ちにこの契約を解約できます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ア　事業者が、正当な理由なく本契約に定めるサービスを提供せず、利用者の請求にもかかわらず、これを提供しようとしない場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　イ　事業者が、12に定める守秘義務に違反した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ウ　事業者が、利用者の身体・財産・名誉等を傷つけ、又は著しい不信行為を行うなど、本契約を継続しがたい重大な事由が認められる場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>9 事業者の解約権</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>(1) 事業者は、次のいずれかに該当する場合は、文書により2週間以上の予告期間をもって、この契約を解約することができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ア　利用者が故意に法令違反その他著しく常識を逸脱する行為をなし、事業者の再三の申し入れにもかかわらず改善の見込みがなく、本契約の目的を達することが著しく困難となった場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　イ　利用者が事業者の通常の事業の実施地域外に転居し、事業者においてサービスの提供の継続が困難であると見込まれる場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="45" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>(2) 事業者は、9の(1)によりこの契約を解約する場合には、担当の地域包括支援センター及び必要に応じて関係市町村に連絡を取り、解約後も利用者の健康や生命に支障のないよう、必要な措置を講じます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>10 契約の終了</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>次のいずれかに該当する場合は、この契約は終了します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>(1) 2の(2)の規定により利用者から契約更新しない旨の申出があり、契約期間が満了した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>(2) 8の(1)の規定により利用者から解約の意思表示がなされ、予告期間が満了した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>(3) 6又は8の(2)の規定により利用者から解約の意思表示がなされた場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>(4) 7の規定により事業者から解約の意思表示がなされた場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>(5) 9の規定により事業者から解約の意思表示がなされ、予告期間が満了した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>(6) 利用者が介護保険施設へ入所した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>(7) 利用者が介護予防特定施設入居者生活介護、介護予防認知症対応型共同生活介護、介護予防小規模多機能型居宅介護又は看護小規模多機能型居宅介護を受けることとなった場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>(8) 利用者の要介護状態区分が自立又は要介護となった場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>(9) 利用者が死亡した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>11 損害賠償</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>(1) 事業者は、サービスの提供にあたり、利用者又は利用者の家族の生命・身体・財産に損害が発生した場合は、速やかに利用者又は利用者の家族に対して損害を賠償します。ただし、当該損害について事業者の責任を問えない場合はこの限りではありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>(2) 前項の義務履行を確保するため、事業者は損害賠償保険に加入します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>(3) 利用者又は利用者の家族に重大な過失がある場合、賠償額を減額することができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>12 守秘義務</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>(1) 事業者及び事業者の従事者は、サービスの提供にあたって知り得た利用者又は利用者の家族の秘密及び個人情報について、正当な理由がない限り、契約中及び契約終了後においても、第三者には漏らしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>(2) 事業者は、事業者の従業員が退職後、在職中に知り得た利用者又は利用者の家族の秘密及び個人情報を漏らすことがないよう必要な処置を講じます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="45" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>(3) 事業者は、利用者及び利用者の家族の個人情報について、介護保険法第23条の規定によるもののほか、利用者の介護予防ケアプラン立案のためのサービス担当者会議並びに地域包括支援センター及び介護予防サービス事業者等との連絡調整において必要な場合に限り、必要最小限の範囲内で使用します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>(4) 12の(1)の規定にかかわらず、事業者は、高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律（平成17年法律第124号）に定める通報ができるものとし、その場合、事業者は秘密保持義務違反の責任を負わないものとします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>13 苦情処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>(1) 利用者又は利用者の家族は、提供されたサービスに苦情がある場合は、「契約書別紙（兼重要事項説明書）」に記載された事業者の相談窓口及び関係機関に対して、いつでも苦情を申し立てることができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>(2) 事業者は、提供したサービスについて、利用者又は利用者の家族から苦情の申出があった場合は、迅速かつ適切に対処し、サービスの向上及び改善に努めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>(3) 事業者は、利用者が苦情申立を行った場合、これを理由としていかなる不利益な扱いもいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>14 サービス内容等の記録の作成及び保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>(1) 事業者は、サービスの提供に関する記録を整備し、完結の日から5年間保存します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="45" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>(2) 利用者及び利用者の後見人（必要に応じ、利用者の家族を含む。）は、事業者に対し、いつでも前項の記録の閲覧及び複写を求めることができます。ただし、複写に際しては、事業者は利用者に対して、実費相当額を請求できるものとします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="45" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>(3) 事業者は、契約の終了にあたって必要があると認められる場合は、利用者の同意を得た上で、利用者の指定する他の居宅介護支援事業者等へ、14の(1)の記録の写しを交付することができるものとします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>15 契約外条項</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>(1) 本契約に定めのない事項については、介護保険法その他関係法令の定めるところを尊重し、利用者及び事業者の協議により定めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>以上のとおり、介護予防・日常生活支援総合事業第1号事業に関する契約を締結します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>上記契約を証するため、本書2通を作成し、利用者及び事業者の双方が記名・押印の上、それぞれ1部ずつ保有します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>契約締結日</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>令和　　年　　月　　日</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="n"/>
-      <c r="D90" s="12" t="n"/>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>（利用者）私は、この契約内容に同意し、サービスの利用を申し込みます。また、12の(3)に定める利用者の個人情報の使用について、同意します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>住所</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr"/>
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr"/>
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>印</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>（代理人）私は、利用者本人の契約の意思を確認の上、本人に代わり、上記署名を行いました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>署名代行者 住所</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr"/>
-      <c r="C97" s="12" t="n"/>
-      <c r="D97" s="12" t="n"/>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr"/>
-      <c r="C98" s="12" t="n"/>
-      <c r="D98" s="12" t="n"/>
-      <c r="E98" s="13" t="inlineStr">
-        <is>
-          <t>印</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>（事業者）私は、利用者の申込みを受託し、この契約書に定める各種サービスを、誠実に責任をもって行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>事業者 所在地</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="inlineStr">
-        <is>
-          <t>〒541-0058 大阪市中央区南久宝寺町四丁目5番17号 アップウェル船場 2F</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>事業者名</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="n"/>
-      <c r="D102" s="12" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>代表者職・氏名</t>
-        </is>
-      </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t>代表取締役　吉田 駿成</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n"/>
-      <c r="D103" s="12" t="n"/>
-      <c r="E103" s="13" t="inlineStr">
-        <is>
-          <t>印</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>（立会人）私は、（※利用者との続柄）として、この契約に立ち会いました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t>住所</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="inlineStr"/>
-      <c r="C106" s="12" t="n"/>
-      <c r="D106" s="12" t="n"/>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr"/>
-      <c r="C107" s="12" t="n"/>
-      <c r="D107" s="12" t="n"/>
-      <c r="E107" s="13" t="inlineStr">
-        <is>
-          <t>印</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>続柄</t>
-        </is>
-      </c>
-      <c r="B108" s="11" t="inlineStr"/>
-      <c r="C108" s="12" t="n"/>
-      <c r="D108" s="12" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="86">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A96:E96"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A92:E92"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="88" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12402,7 +10763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12924,7 +11285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13690,7 +12051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14309,7 +12670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14972,7 +13333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15434,4 +13795,844 @@
     <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E146"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>休暇規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に付与される休暇に関する事項を定め、労働基準法その他関係法令を遵守しつつ、従業員の心身の健康保持と円滑な業務運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、嘱託社員、短時間勤務者、アルバイト等については、就業形態に応じて別途定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>第2章　年次有給休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>（付与要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>第3条　会社は、継続勤務6か月を経過し、その期間の全労働日の8割以上出勤した従業員に対し、10日の年次有給休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>（取得方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>（時季変更権）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>（時間単位年休）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>（計画的付与）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>（年5日の取得義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>（有効期限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="28" t="inlineStr"/>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="12" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="12" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>第3章　特別休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="26" t="inlineStr">
+        <is>
+          <t>（慶弔休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>1　本人の結婚：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>2　子女の結婚：2日</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>3　配偶者の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>4　父母・子の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>6　その他会社が必要と認めた場合：別途定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
+          <t>（産前産後休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="8" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>（育児休業・介護休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="26" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇・介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>（病気休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>（公務・公用休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>（感染症予防に伴う休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>（生理休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>（育児時間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>（母性健康管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="26" t="inlineStr">
+        <is>
+          <t>（誕生日休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="8" customHeight="1"/>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>（その他の特別休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="8" customHeight="1"/>
+    <row r="114" ht="8" customHeight="1">
+      <c r="A114" s="28" t="inlineStr"/>
+      <c r="B114" s="12" t="n"/>
+      <c r="C114" s="12" t="n"/>
+      <c r="D114" s="12" t="n"/>
+      <c r="E114" s="12" t="n"/>
+    </row>
+    <row r="115" ht="10" customHeight="1"/>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="25" t="inlineStr">
+        <is>
+          <t>第4章　手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>（申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="26" t="inlineStr">
+        <is>
+          <t>（診断書等の提出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>1　私傷病により連続して3日以上欠勤するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>2　休職を申請するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="27" t="inlineStr">
+        <is>
+          <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="27" t="inlineStr">
+        <is>
+          <t>5　会社が安全衛生管理上必要と認めたとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="28" t="inlineStr"/>
+      <c r="B133" s="12" t="n"/>
+      <c r="C133" s="12" t="n"/>
+      <c r="D133" s="12" t="n"/>
+      <c r="E133" s="12" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="25" t="inlineStr">
+        <is>
+          <t>第5章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="26" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="26" t="inlineStr">
+        <is>
+          <t>（休暇中の待遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="32" customHeight="1">
+      <c r="A140" s="27" t="inlineStr">
+        <is>
+          <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="8" customHeight="1">
+      <c r="A142" s="28" t="inlineStr"/>
+      <c r="B142" s="12" t="n"/>
+      <c r="C142" s="12" t="n"/>
+      <c r="D142" s="12" t="n"/>
+      <c r="E142" s="12" t="n"/>
+    </row>
+    <row r="143" ht="10" customHeight="1"/>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="25" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="27" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="27" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="94">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　休暇規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
 </file>